--- a/data/nursery_school/data(2).xlsx
+++ b/data/nursery_school/data(2).xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R120"/>
+  <dimension ref="A1:R123"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1598,7 +1598,7 @@
         <v>https://kagawa-colorful.com/hoikusyo/h28/</v>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>令和11年4月から、「川東こども園」と統合予定</v>
       </c>
       <c r="I22" t="str">
         <v>認定公立保育所</v>
@@ -1810,22 +1810,22 @@
         <v>134.140155</v>
       </c>
       <c r="D26" t="str">
-        <v>高松市立田井保育所</v>
+        <v>旧高松市立田井保育所</v>
       </c>
       <c r="E26" t="str">
         <v>高松市牟礼町牟礼100-1</v>
       </c>
       <c r="F26" t="str">
-        <v>087-845-5411</v>
+        <v/>
       </c>
       <c r="G26" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h32/</v>
+        <v/>
       </c>
       <c r="H26" t="str">
         <v/>
       </c>
       <c r="I26" t="str">
-        <v>認定公立保育所</v>
+        <v/>
       </c>
       <c r="J26" t="str">
         <v/>
@@ -1834,19 +1834,19 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>80</v>
+        <v/>
       </c>
       <c r="M26" t="str">
-        <v>3か月～</v>
+        <v/>
       </c>
       <c r="N26" t="str">
-        <v>月火水木金土</v>
+        <v/>
       </c>
       <c r="O26" t="str">
-        <v>07:30</v>
+        <v/>
       </c>
       <c r="P26" t="str">
-        <v>18:30</v>
+        <v/>
       </c>
       <c r="Q26" t="str">
         <v/>
@@ -2412,7 +2412,7 @@
         <v/>
       </c>
       <c r="R36" t="str">
-        <v/>
+        <v>有</v>
       </c>
     </row>
     <row r="37">
@@ -2420,28 +2420,28 @@
         <v>40</v>
       </c>
       <c r="B37" t="str">
-        <v>34.420292</v>
+        <v>34.344356</v>
       </c>
       <c r="C37" t="str">
-        <v>134.057016</v>
+        <v>134.137129</v>
       </c>
       <c r="D37" t="str">
-        <v>高松市小規模保育事業所男木保育所</v>
+        <v>高松市田井こども園</v>
       </c>
       <c r="E37" t="str">
-        <v>高松市男木町165</v>
+        <v>高松市牟礼町牟礼1243-2</v>
       </c>
       <c r="F37" t="str">
-        <v>087-873-0614</v>
+        <v>087-845-5411</v>
       </c>
       <c r="G37" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/%25E9%25AB%2598%25E6%259D%25BE%25E5%25B8%2582%25E5%25B0%258F%25E8%25A6%258F%25E6%25A8%25A1%25E4%25BF%259D%25E8%2582%25B2%25E4%25BA%258B%25E6%25A5%25AD%25E6%2589%2580%25E3%2580%2580%25E7%2594%25B7%25E6%259C%25A8%25E4%25BF%259D%25E8%2582%25B2%25E6%2589%2580%25EF%25BC%2592/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h362/</v>
       </c>
       <c r="H37" t="str">
         <v/>
       </c>
       <c r="I37" t="str">
-        <v>小規模保育施設</v>
+        <v>認定こども園（幼保連携型）</v>
       </c>
       <c r="J37" t="str">
         <v/>
@@ -2450,25 +2450,25 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>6</v>
+        <v>1号認定 15、2・3号認定 80</v>
       </c>
       <c r="M37" t="str">
-        <v>1歳児～</v>
+        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
       </c>
       <c r="N37" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O37" t="str">
-        <v>09:00</v>
+        <v>07:30</v>
       </c>
       <c r="P37" t="str">
-        <v>16:00</v>
+        <v>18:30</v>
       </c>
       <c r="Q37" t="str">
         <v/>
       </c>
       <c r="R37" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="38">
@@ -2476,28 +2476,28 @@
         <v>41</v>
       </c>
       <c r="B38" t="str">
-        <v>34.327973</v>
+        <v>34.420292</v>
       </c>
       <c r="C38" t="str">
-        <v>134.058101</v>
+        <v>134.057016</v>
       </c>
       <c r="D38" t="str">
-        <v>こぶし今里保育園</v>
+        <v>高松市小規模保育事業所男木保育所</v>
       </c>
       <c r="E38" t="str">
-        <v>高松市今里町一丁目7-2</v>
+        <v>高松市男木町165</v>
       </c>
       <c r="F38" t="str">
-        <v>087-834-1946</v>
+        <v>087-873-0614</v>
       </c>
       <c r="G38" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h159/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/%25E9%25AB%2598%25E6%259D%25BE%25E5%25B8%2582%25E5%25B0%258F%25E8%25A6%258F%25E6%25A8%25A1%25E4%25BF%259D%25E8%2582%25B2%25E4%25BA%258B%25E6%25A5%25AD%25E6%2589%2580%25E3%2580%2580%25E7%2594%25B7%25E6%259C%25A8%25E4%25BF%259D%25E8%2582%25B2%25E6%2589%2580%25EF%25BC%2592/</v>
       </c>
       <c r="H38" t="str">
         <v/>
       </c>
       <c r="I38" t="str">
-        <v>認定私立保育所</v>
+        <v>小規模保育施設</v>
       </c>
       <c r="J38" t="str">
         <v/>
@@ -2506,25 +2506,25 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="M38" t="str">
-        <v>2か月～</v>
+        <v>1歳児～</v>
       </c>
       <c r="N38" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O38" t="str">
-        <v>07:00</v>
+        <v>09:00</v>
       </c>
       <c r="P38" t="str">
-        <v>19:00</v>
+        <v>16:00</v>
       </c>
       <c r="Q38" t="str">
         <v/>
       </c>
       <c r="R38" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="39">
@@ -2532,22 +2532,22 @@
         <v>42</v>
       </c>
       <c r="B39" t="str">
-        <v>34.333037</v>
+        <v>34.327973</v>
       </c>
       <c r="C39" t="str">
-        <v>134.051372</v>
+        <v>134.058101</v>
       </c>
       <c r="D39" t="str">
-        <v>敬愛保育園</v>
+        <v>こぶし今里保育園</v>
       </c>
       <c r="E39" t="str">
-        <v>高松市藤塚町三丁目18-2</v>
+        <v>高松市今里町一丁目7-2</v>
       </c>
       <c r="F39" t="str">
-        <v>087-831-6778</v>
+        <v>087-834-1946</v>
       </c>
       <c r="G39" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h33/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h159/</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -2562,10 +2562,10 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="M39" t="str">
-        <v>3か月～</v>
+        <v>2か月～</v>
       </c>
       <c r="N39" t="str">
         <v>月火水木金土</v>
@@ -2580,7 +2580,7 @@
         <v/>
       </c>
       <c r="R39" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="40">
@@ -2588,22 +2588,22 @@
         <v>43</v>
       </c>
       <c r="B40" t="str">
-        <v>34.328268</v>
+        <v>34.333037</v>
       </c>
       <c r="C40" t="str">
-        <v>134.066087</v>
+        <v>134.051372</v>
       </c>
       <c r="D40" t="str">
-        <v>平安保育園</v>
+        <v>敬愛保育園</v>
       </c>
       <c r="E40" t="str">
-        <v>高松市上福岡町894-8</v>
+        <v>高松市藤塚町三丁目18-2</v>
       </c>
       <c r="F40" t="str">
-        <v>087-833-7734</v>
+        <v>087-831-6778</v>
       </c>
       <c r="G40" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h160/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h33/</v>
       </c>
       <c r="H40" t="str">
         <v/>
@@ -2618,10 +2618,10 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="M40" t="str">
-        <v>2か月～</v>
+        <v>3か月～</v>
       </c>
       <c r="N40" t="str">
         <v>月火水木金土</v>
@@ -2644,28 +2644,28 @@
         <v>44</v>
       </c>
       <c r="B41" t="str">
-        <v>34.304804</v>
+        <v>34.328268</v>
       </c>
       <c r="C41" t="str">
-        <v>134.02164</v>
+        <v>134.066087</v>
       </c>
       <c r="D41" t="str">
-        <v>幼保連携型認定こども園　勅使百華こども園</v>
+        <v>平安保育園</v>
       </c>
       <c r="E41" t="str">
-        <v>高松市勅使町955</v>
+        <v>高松市上福岡町894-8</v>
       </c>
       <c r="F41" t="str">
-        <v>087-865-2998</v>
+        <v>087-833-7734</v>
       </c>
       <c r="G41" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h340/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h160/</v>
       </c>
       <c r="H41" t="str">
         <v/>
       </c>
       <c r="I41" t="str">
-        <v>認定こども園（幼保連携型）</v>
+        <v>認定私立保育所</v>
       </c>
       <c r="J41" t="str">
         <v/>
@@ -2674,10 +2674,10 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>1号認定 15、2・3号認定 220</v>
+        <v>130</v>
       </c>
       <c r="M41" t="str">
-        <v>1号認定 満3歳～、2・3号認定 ３か月～</v>
+        <v>2か月～</v>
       </c>
       <c r="N41" t="str">
         <v>月火水木金土</v>
@@ -2692,7 +2692,7 @@
         <v/>
       </c>
       <c r="R41" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="42">
@@ -2700,28 +2700,28 @@
         <v>45</v>
       </c>
       <c r="B42" t="str">
-        <v>34.316835</v>
+        <v>34.304804</v>
       </c>
       <c r="C42" t="str">
-        <v>134.024336</v>
+        <v>134.02164</v>
       </c>
       <c r="D42" t="str">
-        <v>西春日保育所</v>
+        <v>幼保連携型認定こども園　勅使百華こども園</v>
       </c>
       <c r="E42" t="str">
-        <v>高松市西春日町1407</v>
+        <v>高松市勅使町955</v>
       </c>
       <c r="F42" t="str">
-        <v>087-866-4166</v>
+        <v>087-865-2998</v>
       </c>
       <c r="G42" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h161/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h340/</v>
       </c>
       <c r="H42" t="str">
         <v/>
       </c>
       <c r="I42" t="str">
-        <v>認定私立保育所</v>
+        <v>認定こども園（幼保連携型）</v>
       </c>
       <c r="J42" t="str">
         <v/>
@@ -2730,10 +2730,10 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>120</v>
+        <v>1号認定 15、2・3号認定 220</v>
       </c>
       <c r="M42" t="str">
-        <v>2か月～</v>
+        <v>1号認定 満3歳～、2・3号認定 ３か月～</v>
       </c>
       <c r="N42" t="str">
         <v>月火水木金土</v>
@@ -2756,22 +2756,22 @@
         <v>46</v>
       </c>
       <c r="B43" t="str">
-        <v>34.304304</v>
+        <v>34.316835</v>
       </c>
       <c r="C43" t="str">
-        <v>134.037996</v>
+        <v>134.024336</v>
       </c>
       <c r="D43" t="str">
-        <v>らく楽太田保育園</v>
+        <v>西春日保育所</v>
       </c>
       <c r="E43" t="str">
-        <v>高松市太田下町2025</v>
+        <v>高松市西春日町1407</v>
       </c>
       <c r="F43" t="str">
-        <v>087-865-0601</v>
+        <v>087-866-4166</v>
       </c>
       <c r="G43" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h162/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h161/</v>
       </c>
       <c r="H43" t="str">
         <v/>
@@ -2786,10 +2786,10 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="M43" t="str">
-        <v>3か月～</v>
+        <v>2か月～</v>
       </c>
       <c r="N43" t="str">
         <v>月火水木金土</v>
@@ -2804,7 +2804,7 @@
         <v/>
       </c>
       <c r="R43" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="44">
@@ -2812,22 +2812,22 @@
         <v>47</v>
       </c>
       <c r="B44" t="str">
-        <v>34.309654</v>
+        <v>34.304304</v>
       </c>
       <c r="C44" t="str">
-        <v>134.0631</v>
+        <v>134.037996</v>
       </c>
       <c r="D44" t="str">
-        <v>こぶし中央保育園</v>
+        <v>らく楽太田保育園</v>
       </c>
       <c r="E44" t="str">
-        <v>高松市木太町5089-9</v>
+        <v>高松市太田下町2025</v>
       </c>
       <c r="F44" t="str">
-        <v>087-866-7169</v>
+        <v>087-865-0601</v>
       </c>
       <c r="G44" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h35/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h162/</v>
       </c>
       <c r="H44" t="str">
         <v/>
@@ -2842,10 +2842,10 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="M44" t="str">
-        <v>2か月～</v>
+        <v>3か月～</v>
       </c>
       <c r="N44" t="str">
         <v>月火水木金土</v>
@@ -2860,7 +2860,7 @@
         <v/>
       </c>
       <c r="R44" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="45">
@@ -2868,22 +2868,22 @@
         <v>48</v>
       </c>
       <c r="B45" t="str">
-        <v>34.350107</v>
+        <v>34.309654</v>
       </c>
       <c r="C45" t="str">
-        <v>134.091559</v>
+        <v>134.0631</v>
       </c>
       <c r="D45" t="str">
-        <v>あすなろ保育園</v>
+        <v>こぶし中央保育園</v>
       </c>
       <c r="E45" t="str">
-        <v>高松市屋島西町2453-6</v>
+        <v>高松市木太町5089-9</v>
       </c>
       <c r="F45" t="str">
-        <v>087-843-3143</v>
+        <v>087-866-7169</v>
       </c>
       <c r="G45" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h36/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h35/</v>
       </c>
       <c r="H45" t="str">
         <v/>
@@ -2898,10 +2898,10 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="M45" t="str">
-        <v>3か月～</v>
+        <v>2か月～</v>
       </c>
       <c r="N45" t="str">
         <v>月火水木金土</v>
@@ -2916,7 +2916,7 @@
         <v/>
       </c>
       <c r="R45" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="46">
@@ -2924,28 +2924,28 @@
         <v>49</v>
       </c>
       <c r="B46" t="str">
-        <v>34.300415</v>
+        <v>34.350107</v>
       </c>
       <c r="C46" t="str">
-        <v>134.115798</v>
+        <v>134.091559</v>
       </c>
       <c r="D46" t="str">
-        <v>認定こども園　西光寺保育園</v>
+        <v>あすなろ保育園</v>
       </c>
       <c r="E46" t="str">
-        <v>高松市前田西町167-1</v>
+        <v>高松市屋島西町2453-6</v>
       </c>
       <c r="F46" t="str">
-        <v>087-847-6237</v>
+        <v>087-843-3143</v>
       </c>
       <c r="G46" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h330/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h36/</v>
       </c>
       <c r="H46" t="str">
         <v/>
       </c>
       <c r="I46" t="str">
-        <v>認定こども園（幼保連携型）</v>
+        <v>認定私立保育所</v>
       </c>
       <c r="J46" t="str">
         <v/>
@@ -2954,10 +2954,10 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>1号認定 15、2・3号認定 107</v>
+        <v>150</v>
       </c>
       <c r="M46" t="str">
-        <v>1号認定 3歳児～、2・3号認定 2か月～</v>
+        <v>3か月～</v>
       </c>
       <c r="N46" t="str">
         <v>月火水木金土</v>
@@ -2980,22 +2980,22 @@
         <v>50</v>
       </c>
       <c r="B47" t="str">
-        <v>34.299537</v>
+        <v>34.300415</v>
       </c>
       <c r="C47" t="str">
-        <v>134.092378</v>
+        <v>134.115798</v>
       </c>
       <c r="D47" t="str">
-        <v>幼保連携型認定こども園　川添こども園</v>
+        <v>認定こども園　西光寺保育園</v>
       </c>
       <c r="E47" t="str">
-        <v>高松市下田井町52</v>
+        <v>高松市前田西町167-1</v>
       </c>
       <c r="F47" t="str">
-        <v>087-847-5078</v>
+        <v>087-847-6237</v>
       </c>
       <c r="G47" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h331/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h330/</v>
       </c>
       <c r="H47" t="str">
         <v/>
@@ -3010,10 +3010,10 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>1号認定 15、2・3号認定 105</v>
+        <v>1号認定 15、2・3号認定 107</v>
       </c>
       <c r="M47" t="str">
-        <v>1号認定 満3歳～、2・3号認定 ３か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 2か月～</v>
       </c>
       <c r="N47" t="str">
         <v>月火水木金土</v>
@@ -3033,31 +3033,31 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B48" t="str">
-        <v>34.277465</v>
+        <v>34.299537</v>
       </c>
       <c r="C48" t="str">
-        <v>134.030037</v>
+        <v>134.092378</v>
       </c>
       <c r="D48" t="str">
-        <v>高松南保育園</v>
+        <v>幼保連携型認定こども園　川添こども園</v>
       </c>
       <c r="E48" t="str">
-        <v>高松市寺井町453-1</v>
+        <v>高松市下田井町52</v>
       </c>
       <c r="F48" t="str">
-        <v>087-886-0275</v>
+        <v>087-847-5078</v>
       </c>
       <c r="G48" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h38/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h331/</v>
       </c>
       <c r="H48" t="str">
         <v/>
       </c>
       <c r="I48" t="str">
-        <v>認定私立保育所</v>
+        <v>認定こども園（幼保連携型）</v>
       </c>
       <c r="J48" t="str">
         <v/>
@@ -3066,10 +3066,10 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>160</v>
+        <v>1号認定 15、2・3号認定 105</v>
       </c>
       <c r="M48" t="str">
-        <v>6か月～</v>
+        <v>1号認定 満3歳～、2・3号認定 ３か月～</v>
       </c>
       <c r="N48" t="str">
         <v>月火水木金土</v>
@@ -3089,31 +3089,31 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B49" t="str">
-        <v>34.284927</v>
+        <v>34.277465</v>
       </c>
       <c r="C49" t="str">
-        <v>134.010137</v>
+        <v>134.030037</v>
       </c>
       <c r="D49" t="str">
-        <v>幼保連携型　円座百華こども園</v>
+        <v>高松南保育園</v>
       </c>
       <c r="E49" t="str">
-        <v>高松市円座町1478-1</v>
+        <v>高松市寺井町453-1</v>
       </c>
       <c r="F49" t="str">
-        <v>087-885-1203</v>
+        <v>087-886-0275</v>
       </c>
       <c r="G49" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h332/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h38/</v>
       </c>
       <c r="H49" t="str">
         <v/>
       </c>
       <c r="I49" t="str">
-        <v>認定こども園（幼保連携型）</v>
+        <v>認定私立保育所</v>
       </c>
       <c r="J49" t="str">
         <v/>
@@ -3122,10 +3122,10 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>1号認定 15、2・3号認定 250</v>
+        <v>160</v>
       </c>
       <c r="M49" t="str">
-        <v>1号認定 満3歳～、2・3号認定 ３か月～</v>
+        <v>6か月～</v>
       </c>
       <c r="N49" t="str">
         <v>月火水木金土</v>
@@ -3134,7 +3134,7 @@
         <v>07:00</v>
       </c>
       <c r="P49" t="str">
-        <v>19:00</v>
+        <v>18:30</v>
       </c>
       <c r="Q49" t="str">
         <v/>
@@ -3145,31 +3145,31 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B50" t="str">
-        <v>34.306205</v>
+        <v>34.284927</v>
       </c>
       <c r="C50" t="str">
-        <v>133.998614</v>
+        <v>134.010137</v>
       </c>
       <c r="D50" t="str">
-        <v>高松西保育園</v>
+        <v>幼保連携型　円座百華こども園</v>
       </c>
       <c r="E50" t="str">
-        <v>高松市檀紙町1521-4</v>
+        <v>高松市円座町1478-1</v>
       </c>
       <c r="F50" t="str">
-        <v>087-886-5006</v>
+        <v>087-885-1203</v>
       </c>
       <c r="G50" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h40/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h332/</v>
       </c>
       <c r="H50" t="str">
         <v/>
       </c>
       <c r="I50" t="str">
-        <v>認定私立保育所</v>
+        <v>認定こども園（幼保連携型）</v>
       </c>
       <c r="J50" t="str">
         <v/>
@@ -3178,10 +3178,10 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>130</v>
+        <v>1号認定 15、2・3号認定 250</v>
       </c>
       <c r="M50" t="str">
-        <v>3か月～</v>
+        <v>1号認定 満3歳～、2・3号認定 ３か月～</v>
       </c>
       <c r="N50" t="str">
         <v>月火水木金土</v>
@@ -3201,25 +3201,25 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B51" t="str">
-        <v>34.285075</v>
+        <v>34.306205</v>
       </c>
       <c r="C51" t="str">
-        <v>134.110374</v>
+        <v>133.998614</v>
       </c>
       <c r="D51" t="str">
-        <v>若葉保育園</v>
+        <v>高松西保育園</v>
       </c>
       <c r="E51" t="str">
-        <v>高松市亀田南町108-2</v>
+        <v>高松市檀紙町1521-4</v>
       </c>
       <c r="F51" t="str">
-        <v>087-847-7932</v>
+        <v>087-886-5006</v>
       </c>
       <c r="G51" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h168/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h40/</v>
       </c>
       <c r="H51" t="str">
         <v/>
@@ -3237,7 +3237,7 @@
         <v>130</v>
       </c>
       <c r="M51" t="str">
-        <v>3か月～</v>
+        <v>6か月～</v>
       </c>
       <c r="N51" t="str">
         <v>月火水木金土</v>
@@ -3246,7 +3246,7 @@
         <v>07:00</v>
       </c>
       <c r="P51" t="str">
-        <v>19:00</v>
+        <v>18:30</v>
       </c>
       <c r="Q51" t="str">
         <v/>
@@ -3257,25 +3257,25 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B52" t="str">
-        <v>34.311827</v>
+        <v>34.285075</v>
       </c>
       <c r="C52" t="str">
-        <v>134.08609</v>
+        <v>134.110374</v>
       </c>
       <c r="D52" t="str">
-        <v>白樺保育園</v>
+        <v>若葉保育園</v>
       </c>
       <c r="E52" t="str">
-        <v>高松市元山町855-2</v>
+        <v>高松市亀田南町108-2</v>
       </c>
       <c r="F52" t="str">
-        <v>087-866-6555</v>
+        <v>087-847-7932</v>
       </c>
       <c r="G52" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h41/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h168/</v>
       </c>
       <c r="H52" t="str">
         <v/>
@@ -3290,7 +3290,7 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="M52" t="str">
         <v>3か月～</v>
@@ -3313,25 +3313,25 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B53" t="str">
-        <v>34.320782</v>
+        <v>34.311827</v>
       </c>
       <c r="C53" t="str">
-        <v>134.067903</v>
+        <v>134.08609</v>
       </c>
       <c r="D53" t="str">
-        <v>さくらんぼ保育園</v>
+        <v>白樺保育園</v>
       </c>
       <c r="E53" t="str">
-        <v>高松市木太町1165-3</v>
+        <v>高松市元山町855-2</v>
       </c>
       <c r="F53" t="str">
-        <v>087-867-4151</v>
+        <v>087-866-6555</v>
       </c>
       <c r="G53" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h43/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h41/</v>
       </c>
       <c r="H53" t="str">
         <v/>
@@ -3346,16 +3346,16 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="M53" t="str">
-        <v>1歳～</v>
+        <v>3か月～</v>
       </c>
       <c r="N53" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O53" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P53" t="str">
         <v>19:00</v>
@@ -3369,25 +3369,25 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B54" t="str">
-        <v>34.263658</v>
+        <v>34.320782</v>
       </c>
       <c r="C54" t="str">
-        <v>134.108531</v>
+        <v>134.067903</v>
       </c>
       <c r="D54" t="str">
-        <v>すみれ保育園</v>
+        <v>さくらんぼ保育園</v>
       </c>
       <c r="E54" t="str">
-        <v>高松市十川東町556-1</v>
+        <v>高松市木太町1165-3</v>
       </c>
       <c r="F54" t="str">
-        <v>087-848-0806</v>
+        <v>087-867-4151</v>
       </c>
       <c r="G54" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h169/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h43/</v>
       </c>
       <c r="H54" t="str">
         <v/>
@@ -3402,16 +3402,16 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="M54" t="str">
-        <v>3か月～</v>
+        <v>1歳～</v>
       </c>
       <c r="N54" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O54" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P54" t="str">
         <v>19:00</v>
@@ -3425,25 +3425,25 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B55" t="str">
-        <v>34.343745</v>
+        <v>34.263658</v>
       </c>
       <c r="C55" t="str">
-        <v>134.052287</v>
+        <v>134.108531</v>
       </c>
       <c r="D55" t="str">
-        <v>高松第二保育園</v>
+        <v>すみれ保育園</v>
       </c>
       <c r="E55" t="str">
-        <v>高松市御坊町2-2</v>
+        <v>高松市十川東町556-1</v>
       </c>
       <c r="F55" t="str">
-        <v>087-821-5241</v>
+        <v>087-848-0806</v>
       </c>
       <c r="G55" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h44/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h169/</v>
       </c>
       <c r="H55" t="str">
         <v/>
@@ -3458,7 +3458,7 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="M55" t="str">
         <v>3か月～</v>
@@ -3467,10 +3467,10 @@
         <v>月火水木金土</v>
       </c>
       <c r="O55" t="str">
-        <v>8:00</v>
+        <v>07:00</v>
       </c>
       <c r="P55" t="str">
-        <v>26:00</v>
+        <v>19:00</v>
       </c>
       <c r="Q55" t="str">
         <v/>
@@ -3481,25 +3481,25 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B56" t="str">
-        <v>34.327799</v>
+        <v>34.343745</v>
       </c>
       <c r="C56" t="str">
-        <v>134.062199</v>
+        <v>134.052287</v>
       </c>
       <c r="D56" t="str">
-        <v>今里保育所</v>
+        <v>高松第二保育園</v>
       </c>
       <c r="E56" t="str">
-        <v>高松市今里町二丁目1-5</v>
+        <v>高松市御坊町2-2</v>
       </c>
       <c r="F56" t="str">
-        <v>087-834-3535</v>
+        <v>087-821-5241</v>
       </c>
       <c r="G56" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h45/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h44/</v>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -3514,7 +3514,7 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="M56" t="str">
         <v>3か月～</v>
@@ -3523,10 +3523,10 @@
         <v>月火水木金土</v>
       </c>
       <c r="O56" t="str">
-        <v>07:00</v>
+        <v>8:00</v>
       </c>
       <c r="P56" t="str">
-        <v>19:00</v>
+        <v>26:00</v>
       </c>
       <c r="Q56" t="str">
         <v/>
@@ -3537,31 +3537,31 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B57" t="str">
-        <v>34.25728</v>
+        <v>34.327799</v>
       </c>
       <c r="C57" t="str">
-        <v>134.035674</v>
+        <v>134.062199</v>
       </c>
       <c r="D57" t="str">
-        <v>さんさんこども園</v>
+        <v>今里保育所</v>
       </c>
       <c r="E57" t="str">
-        <v>高松市香川町浅野834-1</v>
+        <v>高松市今里町二丁目1-5</v>
       </c>
       <c r="F57" t="str">
-        <v>087-888-6333</v>
+        <v>087-834-3535</v>
       </c>
       <c r="G57" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h357/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h45/</v>
       </c>
       <c r="H57" t="str">
         <v/>
       </c>
       <c r="I57" t="str">
-        <v>認定こども園（幼保連携型）</v>
+        <v>認定私立保育所</v>
       </c>
       <c r="J57" t="str">
         <v/>
@@ -3570,10 +3570,10 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>1号認定 10、2・3号認定 120</v>
+        <v>130</v>
       </c>
       <c r="M57" t="str">
-        <v>1号認定 3歳～、2・3号認定 ３か月～</v>
+        <v>3か月～</v>
       </c>
       <c r="N57" t="str">
         <v>月火水木金土</v>
@@ -3588,36 +3588,36 @@
         <v/>
       </c>
       <c r="R57" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B58" t="str">
-        <v>34.289495</v>
+        <v>34.25728</v>
       </c>
       <c r="C58" t="str">
-        <v>133.952485</v>
+        <v>134.035674</v>
       </c>
       <c r="D58" t="str">
-        <v>らく楽国分寺保育園</v>
+        <v>さんさんこども園</v>
       </c>
       <c r="E58" t="str">
-        <v>高松市国分寺町柏原80</v>
+        <v>高松市香川町浅野834-1</v>
       </c>
       <c r="F58" t="str">
-        <v>087-874-0622</v>
+        <v>087-888-6333</v>
       </c>
       <c r="G58" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h171/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h357/</v>
       </c>
       <c r="H58" t="str">
         <v/>
       </c>
       <c r="I58" t="str">
-        <v>認定私立保育所</v>
+        <v>認定こども園（幼保連携型）</v>
       </c>
       <c r="J58" t="str">
         <v/>
@@ -3626,10 +3626,10 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>80</v>
+        <v>1号認定 10、2・3号認定 120</v>
       </c>
       <c r="M58" t="str">
-        <v>3か月～</v>
+        <v>1号認定 3歳～、2・3号認定 ３か月～</v>
       </c>
       <c r="N58" t="str">
         <v>月火水木金土</v>
@@ -3644,30 +3644,30 @@
         <v/>
       </c>
       <c r="R58" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B59" t="str">
-        <v>34.274113</v>
+        <v>34.289495</v>
       </c>
       <c r="C59" t="str">
-        <v>133.973116</v>
+        <v>133.952485</v>
       </c>
       <c r="D59" t="str">
-        <v>みのり保育園</v>
+        <v>らく楽国分寺保育園</v>
       </c>
       <c r="E59" t="str">
-        <v>高松市国分寺町福家甲1982</v>
+        <v>高松市国分寺町柏原80</v>
       </c>
       <c r="F59" t="str">
-        <v>087-874-4309</v>
+        <v>087-874-0622</v>
       </c>
       <c r="G59" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h172/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h171/</v>
       </c>
       <c r="H59" t="str">
         <v/>
@@ -3682,7 +3682,7 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="M59" t="str">
         <v>3か月～</v>
@@ -3700,30 +3700,30 @@
         <v/>
       </c>
       <c r="R59" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B60" t="str">
-        <v>34.337967</v>
+        <v>34.274113</v>
       </c>
       <c r="C60" t="str">
-        <v>134.130825</v>
+        <v>133.973116</v>
       </c>
       <c r="D60" t="str">
-        <v>八栗保育所</v>
+        <v>みのり保育園</v>
       </c>
       <c r="E60" t="str">
-        <v>高松市牟礼町牟礼401</v>
+        <v>高松市国分寺町福家甲1982</v>
       </c>
       <c r="F60" t="str">
-        <v>087-845-0033</v>
+        <v>087-874-4309</v>
       </c>
       <c r="G60" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h173/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h172/</v>
       </c>
       <c r="H60" t="str">
         <v/>
@@ -3738,19 +3738,19 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="M60" t="str">
-        <v>2か月～</v>
+        <v>3か月～</v>
       </c>
       <c r="N60" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O60" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P60" t="str">
-        <v>18:30</v>
+        <v>19:00</v>
       </c>
       <c r="Q60" t="str">
         <v/>
@@ -3761,25 +3761,25 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B61" t="str">
-        <v>34.347055</v>
+        <v>34.337967</v>
       </c>
       <c r="C61" t="str">
-        <v>134.055965</v>
+        <v>134.130825</v>
       </c>
       <c r="D61" t="str">
-        <v>城東保育園</v>
+        <v>八栗保育所</v>
       </c>
       <c r="E61" t="str">
-        <v>高松市城東町一丁目1-45</v>
+        <v>高松市牟礼町牟礼401</v>
       </c>
       <c r="F61" t="str">
-        <v>087-822-1340</v>
+        <v>087-845-0033</v>
       </c>
       <c r="G61" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h46/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h173/</v>
       </c>
       <c r="H61" t="str">
         <v/>
@@ -3794,7 +3794,7 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M61" t="str">
         <v>2か月～</v>
@@ -3806,7 +3806,7 @@
         <v>07:30</v>
       </c>
       <c r="P61" t="str">
-        <v>19:00</v>
+        <v>18:30</v>
       </c>
       <c r="Q61" t="str">
         <v/>
@@ -3817,25 +3817,25 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B62" t="str">
-        <v>34.334252</v>
+        <v>34.347055</v>
       </c>
       <c r="C62" t="str">
-        <v>134.057679</v>
+        <v>134.055965</v>
       </c>
       <c r="D62" t="str">
-        <v>こぶし花園保育園</v>
+        <v>城東保育園</v>
       </c>
       <c r="E62" t="str">
-        <v>高松市花園町一丁目9-32</v>
+        <v>高松市城東町一丁目1-45</v>
       </c>
       <c r="F62" t="str">
-        <v>087-831-5136</v>
+        <v>087-822-1340</v>
       </c>
       <c r="G62" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h47/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h46/</v>
       </c>
       <c r="H62" t="str">
         <v/>
@@ -3850,7 +3850,7 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M62" t="str">
         <v>2か月～</v>
@@ -3868,36 +3868,36 @@
         <v/>
       </c>
       <c r="R62" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B63" t="str">
-        <v>0</v>
+        <v>34.334252</v>
       </c>
       <c r="C63" t="str">
-        <v>0</v>
+        <v>134.057679</v>
       </c>
       <c r="D63" t="str">
-        <v/>
+        <v>こぶし花園保育園</v>
       </c>
       <c r="E63" t="str">
-        <v/>
+        <v>高松市花園町一丁目9-32</v>
       </c>
       <c r="F63" t="str">
-        <v/>
+        <v>087-831-5136</v>
       </c>
       <c r="G63" t="str">
-        <v/>
+        <v>https://kagawa-colorful.com/hoikusyo/h47/</v>
       </c>
       <c r="H63" t="str">
         <v/>
       </c>
       <c r="I63" t="str">
-        <v/>
+        <v>認定私立保育所</v>
       </c>
       <c r="J63" t="str">
         <v/>
@@ -3906,25 +3906,25 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v/>
+        <v>90</v>
       </c>
       <c r="M63" t="str">
-        <v/>
+        <v>2か月～</v>
       </c>
       <c r="N63" t="str">
-        <v/>
+        <v>月火水木金土</v>
       </c>
       <c r="O63" t="str">
-        <v/>
+        <v>07:30</v>
       </c>
       <c r="P63" t="str">
-        <v/>
+        <v>19:00</v>
       </c>
       <c r="Q63" t="str">
         <v/>
       </c>
       <c r="R63" t="str">
-        <v/>
+        <v>無</v>
       </c>
     </row>
     <row r="64">
@@ -4209,31 +4209,31 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B69" t="str">
-        <v>0</v>
+        <v>34.333051</v>
       </c>
       <c r="C69" t="str">
-        <v>0</v>
+        <v>134.055788</v>
       </c>
       <c r="D69" t="str">
-        <v/>
+        <v>認定こども園　高松くりの木学舎</v>
       </c>
       <c r="E69" t="str">
-        <v/>
+        <v>高松市花園町三丁目4-5</v>
       </c>
       <c r="F69" t="str">
-        <v/>
+        <v>087-880-7211</v>
       </c>
       <c r="G69" t="str">
-        <v/>
+        <v>https://kagawa-colorful.com/hoikusyo/h333/</v>
       </c>
       <c r="H69" t="str">
         <v/>
       </c>
       <c r="I69" t="str">
-        <v/>
+        <v>認定こども園（幼保連携型）</v>
       </c>
       <c r="J69" t="str">
         <v/>
@@ -4242,54 +4242,54 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v/>
+        <v>1号認定 9、2・3号認定 96</v>
       </c>
       <c r="M69" t="str">
-        <v/>
+        <v>1号認定 満3歳～、2・3号認定 3か月～</v>
       </c>
       <c r="N69" t="str">
-        <v/>
+        <v>月火水木金土</v>
       </c>
       <c r="O69" t="str">
-        <v/>
+        <v>07:00</v>
       </c>
       <c r="P69" t="str">
-        <v/>
+        <v>19:00</v>
       </c>
       <c r="Q69" t="str">
         <v/>
       </c>
       <c r="R69" t="str">
-        <v/>
+        <v>有</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B70" t="str">
-        <v>34.333051</v>
+        <v>34.343232</v>
       </c>
       <c r="C70" t="str">
-        <v>134.055788</v>
+        <v>134.065675</v>
       </c>
       <c r="D70" t="str">
-        <v>認定こども園　高松くりの木学舎</v>
+        <v>らく楽第二保育園</v>
       </c>
       <c r="E70" t="str">
-        <v>高松市花園町三丁目4-5</v>
+        <v>高松市松福町二丁目4-4</v>
       </c>
       <c r="F70" t="str">
-        <v>087-880-7211</v>
+        <v>087-826-0111</v>
       </c>
       <c r="G70" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h333/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h269/</v>
       </c>
       <c r="H70" t="str">
         <v/>
       </c>
       <c r="I70" t="str">
-        <v>認定こども園（幼保連携型）</v>
+        <v>認定私立保育所</v>
       </c>
       <c r="J70" t="str">
         <v/>
@@ -4298,16 +4298,16 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>1号認定 9、2・3号認定 96</v>
+        <v>72</v>
       </c>
       <c r="M70" t="str">
-        <v>1号認定 満3歳～、2・3号認定 3か月～</v>
+        <v>3か月～</v>
       </c>
       <c r="N70" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O70" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P70" t="str">
         <v>19:00</v>
@@ -4316,36 +4316,36 @@
         <v/>
       </c>
       <c r="R70" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B71" t="str">
-        <v>34.343232</v>
+        <v>34.291607</v>
       </c>
       <c r="C71" t="str">
-        <v>134.065675</v>
+        <v>134.075471</v>
       </c>
       <c r="D71" t="str">
-        <v>らく楽第二保育園</v>
+        <v>認定こども園あさがおこども園</v>
       </c>
       <c r="E71" t="str">
-        <v>高松市松福町二丁目4-4</v>
+        <v>高松市上林町69</v>
       </c>
       <c r="F71" t="str">
-        <v>087-826-0111</v>
+        <v>087-899-5660</v>
       </c>
       <c r="G71" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h269/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h358/</v>
       </c>
       <c r="H71" t="str">
         <v/>
       </c>
       <c r="I71" t="str">
-        <v>認定私立保育所</v>
+        <v>認定こども園（幼保連携型）</v>
       </c>
       <c r="J71" t="str">
         <v/>
@@ -4354,10 +4354,10 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>72</v>
+        <v>1号認定 9、2・3号認定 131</v>
       </c>
       <c r="M71" t="str">
-        <v>3か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
       </c>
       <c r="N71" t="str">
         <v>月火水木金土</v>
@@ -4372,36 +4372,36 @@
         <v/>
       </c>
       <c r="R71" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B72" t="str">
-        <v>34.291607</v>
+        <v>34.3051941</v>
       </c>
       <c r="C72" t="str">
-        <v>134.075471</v>
+        <v>134.0610552</v>
       </c>
       <c r="D72" t="str">
-        <v>認定こども園あさがおこども園</v>
+        <v>保育園アルペジオ高松多肥下町園</v>
       </c>
       <c r="E72" t="str">
-        <v>高松市上林町69</v>
+        <v>高松市多肥下町1524-15</v>
       </c>
       <c r="F72" t="str">
-        <v>087-899-5660</v>
+        <v>087-802-5583</v>
       </c>
       <c r="G72" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h358/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h288/</v>
       </c>
       <c r="H72" t="str">
         <v/>
       </c>
       <c r="I72" t="str">
-        <v>認定こども園（幼保連携型）</v>
+        <v>認定私立保育所</v>
       </c>
       <c r="J72" t="str">
         <v/>
@@ -4410,10 +4410,10 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>1号認定 9、2・3号認定 131</v>
+        <v>80</v>
       </c>
       <c r="M72" t="str">
-        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
+        <v>満6か月</v>
       </c>
       <c r="N72" t="str">
         <v>月火水木金土</v>
@@ -4433,25 +4433,25 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B73" t="str">
-        <v>34.3051941</v>
+        <v>34.3034175</v>
       </c>
       <c r="C73" t="str">
-        <v>134.0610552</v>
+        <v>134.0533292</v>
       </c>
       <c r="D73" t="str">
-        <v>保育園アルペジオ高松多肥下町園</v>
+        <v>さくら太田保育園</v>
       </c>
       <c r="E73" t="str">
-        <v>高松市多肥下町1524-15</v>
+        <v>高松市太田下町3032-1</v>
       </c>
       <c r="F73" t="str">
-        <v>087-802-5583</v>
+        <v>087-868-3700</v>
       </c>
       <c r="G73" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h288/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h289/</v>
       </c>
       <c r="H73" t="str">
         <v/>
@@ -4466,54 +4466,54 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="M73" t="str">
-        <v>満6か月</v>
+        <v>3か月</v>
       </c>
       <c r="N73" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O73" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P73" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="Q73" t="str">
         <v/>
       </c>
       <c r="R73" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B74" t="str">
-        <v>34.3034175</v>
+        <v>34.3064057</v>
       </c>
       <c r="C74" t="str">
-        <v>134.0533292</v>
+        <v>134.042294</v>
       </c>
       <c r="D74" t="str">
-        <v>さくら太田保育園</v>
+        <v>にこにこ保育園</v>
       </c>
       <c r="E74" t="str">
-        <v>高松市太田下町3032-1</v>
+        <v>高松市林町294-1</v>
       </c>
       <c r="F74" t="str">
-        <v>087-868-3700</v>
+        <v>087-813-8300</v>
       </c>
       <c r="G74" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h289/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h308/</v>
       </c>
       <c r="H74" t="str">
         <v/>
       </c>
       <c r="I74" t="str">
-        <v>認定私立保育所</v>
+        <v>認可私立保育所</v>
       </c>
       <c r="J74" t="str">
         <v/>
@@ -4522,48 +4522,48 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="M74" t="str">
-        <v>3か月</v>
+        <v>2か月～</v>
       </c>
       <c r="N74" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O74" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P74" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="Q74" t="str">
         <v/>
       </c>
       <c r="R74" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B75" t="str">
-        <v>34.3064057</v>
+        <v>34.3047038</v>
       </c>
       <c r="C75" t="str">
-        <v>134.042294</v>
+        <v>134.0565783</v>
       </c>
       <c r="D75" t="str">
-        <v>にこにここども園</v>
+        <v>アイグラン保育園太田</v>
       </c>
       <c r="E75" t="str">
-        <v>高松市林町294-1</v>
+        <v>高松市太田下町3027-4</v>
       </c>
       <c r="F75" t="str">
-        <v>087-813-8300</v>
+        <v>087-802-9065</v>
       </c>
       <c r="G75" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h308/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h312/</v>
       </c>
       <c r="H75" t="str">
         <v/>
@@ -4578,48 +4578,48 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M75" t="str">
-        <v>2か月～</v>
+        <v>３か月～</v>
       </c>
       <c r="N75" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O75" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P75" t="str">
-        <v>19:00</v>
+        <v>20:00</v>
       </c>
       <c r="Q75" t="str">
         <v/>
       </c>
       <c r="R75" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B76" t="str">
-        <v>34.3047038</v>
+        <v>34.3431504</v>
       </c>
       <c r="C76" t="str">
-        <v>134.0565783</v>
+        <v>134.0615252</v>
       </c>
       <c r="D76" t="str">
-        <v>アイグラン保育園太田</v>
+        <v>さくら福々保育園</v>
       </c>
       <c r="E76" t="str">
-        <v>高松市太田下町3027-4</v>
+        <v>高松市松福町一丁目12-7</v>
       </c>
       <c r="F76" t="str">
-        <v>087-802-9065</v>
+        <v>087-802-1860</v>
       </c>
       <c r="G76" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h312/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h322/</v>
       </c>
       <c r="H76" t="str">
         <v/>
@@ -4634,7 +4634,7 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M76" t="str">
         <v>３か月～</v>
@@ -4657,31 +4657,31 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B77" t="str">
-        <v>34.3431504</v>
+        <v>34.292144</v>
       </c>
       <c r="C77" t="str">
-        <v>134.0615252</v>
+        <v>134.066237</v>
       </c>
       <c r="D77" t="str">
-        <v>さくら福々保育園</v>
+        <v>サンシャインこどもの森</v>
       </c>
       <c r="E77" t="str">
-        <v>高松市松福町一丁目12-7</v>
+        <v>高松市上林町502-2</v>
       </c>
       <c r="F77" t="str">
-        <v>087-802-1860</v>
+        <v>087-889-8181</v>
       </c>
       <c r="G77" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h322/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h147/</v>
       </c>
       <c r="H77" t="str">
         <v/>
       </c>
       <c r="I77" t="str">
-        <v>認可私立保育所</v>
+        <v>認定こども園（幼保連携型）</v>
       </c>
       <c r="J77" t="str">
         <v/>
@@ -4690,48 +4690,48 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>96</v>
+        <v>1号認定 15、2・3号認定 105</v>
       </c>
       <c r="M77" t="str">
-        <v>３か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
       </c>
       <c r="N77" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O77" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P77" t="str">
-        <v>20:00</v>
+        <v>19:00</v>
       </c>
       <c r="Q77" t="str">
         <v/>
       </c>
       <c r="R77" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B78" t="str">
-        <v>34.292144</v>
+        <v>34.303319</v>
       </c>
       <c r="C78" t="str">
-        <v>134.066237</v>
+        <v>133.949144</v>
       </c>
       <c r="D78" t="str">
-        <v>サンシャインこどもの森</v>
+        <v>いずみこども園</v>
       </c>
       <c r="E78" t="str">
-        <v>高松市上林町502-2</v>
+        <v>高松市国分寺町国分2408</v>
       </c>
       <c r="F78" t="str">
-        <v>087-889-8181</v>
+        <v>087-874-0882</v>
       </c>
       <c r="G78" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h147/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h148</v>
       </c>
       <c r="H78" t="str">
         <v/>
@@ -4746,19 +4746,19 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>1号認定 15、2・3号認定 105</v>
+        <v>1号認定 15、2・3号認定 85</v>
       </c>
       <c r="M78" t="str">
-        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
+        <v>1号認定 満3歳～、2・3号認定 3か月～</v>
       </c>
       <c r="N78" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O78" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P78" t="str">
-        <v>19:00</v>
+        <v>19:30</v>
       </c>
       <c r="Q78" t="str">
         <v/>
@@ -4769,25 +4769,25 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B79" t="str">
-        <v>34.303319</v>
+        <v>34.304328</v>
       </c>
       <c r="C79" t="str">
-        <v>133.949144</v>
+        <v>133.97246</v>
       </c>
       <c r="D79" t="str">
-        <v>いずみこども園</v>
+        <v>いずみこども園分園</v>
       </c>
       <c r="E79" t="str">
-        <v>高松市国分寺町国分2408</v>
+        <v>高松市国分寺町新居281-1</v>
       </c>
       <c r="F79" t="str">
-        <v>087-874-0882</v>
+        <v>087-875-0882</v>
       </c>
       <c r="G79" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h148</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h211</v>
       </c>
       <c r="H79" t="str">
         <v/>
@@ -4802,19 +4802,19 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>1号認定 15、2・3号認定 85</v>
+        <v>2・3号認定 20</v>
       </c>
       <c r="M79" t="str">
-        <v>1号認定 満3歳～、2・3号認定 3か月～</v>
+        <v>2・3号認定 3か月～２歳児</v>
       </c>
       <c r="N79" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O79" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P79" t="str">
-        <v>19:30</v>
+        <v>18:30</v>
       </c>
       <c r="Q79" t="str">
         <v/>
@@ -4825,25 +4825,25 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B80" t="str">
-        <v>34.304328</v>
+        <v>34.327571</v>
       </c>
       <c r="C80" t="str">
-        <v>133.97246</v>
+        <v>134.087355</v>
       </c>
       <c r="D80" t="str">
-        <v>いずみこども園分園</v>
+        <v>認定こども園高松東幼稚園</v>
       </c>
       <c r="E80" t="str">
-        <v>高松市国分寺町新居281-1</v>
+        <v>高松市春日町688</v>
       </c>
       <c r="F80" t="str">
-        <v>087-875-0882</v>
+        <v>087-841-2306</v>
       </c>
       <c r="G80" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h211</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h262</v>
       </c>
       <c r="H80" t="str">
         <v/>
@@ -4858,48 +4858,48 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>2・3号認定 20</v>
+        <v>1号認定 284、2・3号認定 166</v>
       </c>
       <c r="M80" t="str">
-        <v>2・3号認定 3か月～２歳児</v>
+        <v>1号認定 満3歳～、2・3号認定 3か月～</v>
       </c>
       <c r="N80" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O80" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P80" t="str">
-        <v>18:30</v>
+        <v>19:00</v>
       </c>
       <c r="Q80" t="str">
         <v/>
       </c>
       <c r="R80" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B81" t="str">
-        <v>34.327571</v>
+        <v>34.325356</v>
       </c>
       <c r="C81" t="str">
-        <v>134.087355</v>
+        <v>134.099079</v>
       </c>
       <c r="D81" t="str">
-        <v>認定こども園高松東幼稚園</v>
+        <v>認定こども園新田幼稚園</v>
       </c>
       <c r="E81" t="str">
-        <v>高松市春日町688</v>
+        <v>高松市新田町甲2630-1</v>
       </c>
       <c r="F81" t="str">
-        <v>087-841-2306</v>
+        <v>087-841-3686</v>
       </c>
       <c r="G81" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h262</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h263</v>
       </c>
       <c r="H81" t="str">
         <v/>
@@ -4914,16 +4914,16 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>1号認定 284、2・3号認定 166</v>
+        <v>1号認定 75、2・3号認定 57</v>
       </c>
       <c r="M81" t="str">
-        <v>1号認定 満3歳～、2・3号認定 3か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 6か月～</v>
       </c>
       <c r="N81" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O81" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P81" t="str">
         <v>19:00</v>
@@ -4932,30 +4932,30 @@
         <v/>
       </c>
       <c r="R81" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B82" t="str">
-        <v>34.325356</v>
+        <v>34.268464</v>
       </c>
       <c r="C82" t="str">
-        <v>134.099079</v>
+        <v>134.006758</v>
       </c>
       <c r="D82" t="str">
-        <v>認定こども園新田幼稚園</v>
+        <v>認定こども園和光こども園</v>
       </c>
       <c r="E82" t="str">
-        <v>高松市新田町甲2630-1</v>
+        <v>高松市川部町1561-1</v>
       </c>
       <c r="F82" t="str">
-        <v>087-841-3686</v>
+        <v>087-886-5879</v>
       </c>
       <c r="G82" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h263</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h39/</v>
       </c>
       <c r="H82" t="str">
         <v/>
@@ -4970,16 +4970,16 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>1号認定 75、2・3号認定 57</v>
+        <v>1号認定 15、2・3号認定 100</v>
       </c>
       <c r="M82" t="str">
-        <v>1号認定 3歳児～、2・3号認定 6か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
       </c>
       <c r="N82" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O82" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P82" t="str">
         <v>19:00</v>
@@ -4988,30 +4988,30 @@
         <v/>
       </c>
       <c r="R82" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B83" t="str">
-        <v>34.268464</v>
+        <v>34.331077</v>
       </c>
       <c r="C83" t="str">
-        <v>134.006758</v>
+        <v>134.094275</v>
       </c>
       <c r="D83" t="str">
-        <v>認定こども園和光こども園</v>
+        <v>認定こども園春日こども園</v>
       </c>
       <c r="E83" t="str">
-        <v>高松市川部町1561-1</v>
+        <v>高松市春日町1287-1</v>
       </c>
       <c r="F83" t="str">
-        <v>087-886-5879</v>
+        <v>087-843-3689</v>
       </c>
       <c r="G83" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h39/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h163/</v>
       </c>
       <c r="H83" t="str">
         <v/>
@@ -5026,10 +5026,10 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>1号認定 15、2・3号認定 100</v>
+        <v>1号認定 15、2・3号認定 160</v>
       </c>
       <c r="M83" t="str">
-        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 2か月～</v>
       </c>
       <c r="N83" t="str">
         <v>月火水木金土</v>
@@ -5044,30 +5044,30 @@
         <v/>
       </c>
       <c r="R83" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B84" t="str">
-        <v>34.331077</v>
+        <v>34.326539</v>
       </c>
       <c r="C84" t="str">
-        <v>134.094275</v>
+        <v>134.047837</v>
       </c>
       <c r="D84" t="str">
-        <v>認定こども園春日こども園</v>
+        <v>認定こども園花ノ宮こども園</v>
       </c>
       <c r="E84" t="str">
-        <v>高松市春日町1287-1</v>
+        <v>高松市花ノ宮町一丁目10-22</v>
       </c>
       <c r="F84" t="str">
-        <v>087-843-3689</v>
+        <v>087-831-6318</v>
       </c>
       <c r="G84" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h163/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h175/</v>
       </c>
       <c r="H84" t="str">
         <v/>
@@ -5082,7 +5082,7 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>1号認定 15、2・3号認定 160</v>
+        <v>1号認定 15、2・3号認定 110</v>
       </c>
       <c r="M84" t="str">
         <v>1号認定 3歳児～、2・3号認定 2か月～</v>
@@ -5100,30 +5100,30 @@
         <v/>
       </c>
       <c r="R84" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B85" t="str">
-        <v>34.326539</v>
+        <v>34.333461</v>
       </c>
       <c r="C85" t="str">
-        <v>134.047837</v>
+        <v>134.04506</v>
       </c>
       <c r="D85" t="str">
-        <v>認定こども園花ノ宮こども園</v>
+        <v>認定こども園中野保育所</v>
       </c>
       <c r="E85" t="str">
-        <v>高松市花ノ宮町一丁目10-22</v>
+        <v>高松市中野町27-5</v>
       </c>
       <c r="F85" t="str">
-        <v>087-831-6318</v>
+        <v>087-831-8659</v>
       </c>
       <c r="G85" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h175/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h174/</v>
       </c>
       <c r="H85" t="str">
         <v/>
@@ -5138,48 +5138,48 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>1号認定 15、2・3号認定 110</v>
+        <v>1号認定 15、2・3号認定 160</v>
       </c>
       <c r="M85" t="str">
-        <v>1号認定 3歳児～、2・3号認定 2か月～</v>
+        <v>1号認定 満3歳児～、2・3号認定 3か月～</v>
       </c>
       <c r="N85" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O85" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P85" t="str">
-        <v>19:00</v>
+        <v>19:30</v>
       </c>
       <c r="Q85" t="str">
         <v/>
       </c>
       <c r="R85" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B86" t="str">
-        <v>34.333461</v>
+        <v>34.279891</v>
       </c>
       <c r="C86" t="str">
-        <v>134.04506</v>
+        <v>134.042395</v>
       </c>
       <c r="D86" t="str">
-        <v>認定こども園中野保育所</v>
+        <v>幼保連携型認定こども園カナン保育園</v>
       </c>
       <c r="E86" t="str">
-        <v>高松市中野町27-5</v>
+        <v>高松市仏生山町甲745-2</v>
       </c>
       <c r="F86" t="str">
-        <v>087-831-8659</v>
+        <v>087-889-1059</v>
       </c>
       <c r="G86" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h174/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h166/</v>
       </c>
       <c r="H86" t="str">
         <v/>
@@ -5194,7 +5194,7 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>1号認定 15、2・3号認定 160</v>
+        <v>1号認定 15、2・3号認定 105</v>
       </c>
       <c r="M86" t="str">
         <v>1号認定 満3歳児～、2・3号認定 3か月～</v>
@@ -5203,10 +5203,10 @@
         <v>月火水木金土</v>
       </c>
       <c r="O86" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P86" t="str">
-        <v>19:30</v>
+        <v>19:00</v>
       </c>
       <c r="Q86" t="str">
         <v/>
@@ -5217,25 +5217,25 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B87" t="str">
-        <v>34.279891</v>
+        <v>34.292691</v>
       </c>
       <c r="C87" t="str">
-        <v>134.042395</v>
+        <v>134.0352</v>
       </c>
       <c r="D87" t="str">
-        <v>幼保連携型認定こども園カナン保育園</v>
+        <v>幼保連携型認定こども園すまいる</v>
       </c>
       <c r="E87" t="str">
-        <v>高松市仏生山町甲745-2</v>
+        <v>高松市三名町591-1</v>
       </c>
       <c r="F87" t="str">
-        <v>087-889-1059</v>
+        <v>087-802-3838</v>
       </c>
       <c r="G87" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h166/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h275/</v>
       </c>
       <c r="H87" t="str">
         <v/>
@@ -5250,16 +5250,16 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>1号認定 15、2・3号認定 105</v>
+        <v>1号認定 60、2・3号認定 130</v>
       </c>
       <c r="M87" t="str">
-        <v>1号認定 満3歳児～、2・3号認定 3か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 6か月～</v>
       </c>
       <c r="N87" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O87" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P87" t="str">
         <v>19:00</v>
@@ -5273,25 +5273,25 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B88" t="str">
-        <v>34.292691</v>
+        <v>34.2936161</v>
       </c>
       <c r="C88" t="str">
-        <v>134.0352</v>
+        <v>134.0789214</v>
       </c>
       <c r="D88" t="str">
-        <v>幼保連携型認定こども園すまいる</v>
+        <v>げんき・結愛・げんきこども園</v>
       </c>
       <c r="E88" t="str">
-        <v>高松市三名町591-1</v>
+        <v>高松市六条町604番地7</v>
       </c>
       <c r="F88" t="str">
-        <v>087-802-3838</v>
+        <v>087-813-9818</v>
       </c>
       <c r="G88" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h275/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h37/</v>
       </c>
       <c r="H88" t="str">
         <v/>
@@ -5306,16 +5306,16 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>1号認定 60、2・3号認定 130</v>
+        <v>1号認定 15、2・3号認定 131</v>
       </c>
       <c r="M88" t="str">
-        <v>1号認定 3歳児～、2・3号認定 6か月～</v>
+        <v>1号認定 満3歳児～、2・3号認定 おおむね2か月～</v>
       </c>
       <c r="N88" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O88" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P88" t="str">
         <v>19:00</v>
@@ -5324,30 +5324,30 @@
         <v/>
       </c>
       <c r="R88" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B89" t="str">
-        <v>34.2936161</v>
+        <v>34.2734776</v>
       </c>
       <c r="C89" t="str">
-        <v>134.0789214</v>
+        <v>134.1024882</v>
       </c>
       <c r="D89" t="str">
-        <v>げんき・結愛・げんきこども園</v>
+        <v>幼保連携型カナン十河こども園</v>
       </c>
       <c r="E89" t="str">
-        <v>高松市六条町604番地7</v>
+        <v>高松市十川西町546-1</v>
       </c>
       <c r="F89" t="str">
-        <v>087-813-9818</v>
+        <v>087-848-0320</v>
       </c>
       <c r="G89" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h37/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h48/</v>
       </c>
       <c r="H89" t="str">
         <v/>
@@ -5362,16 +5362,16 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>1号認定 15、2・3号認定 131</v>
+        <v>1号認定 15、2・3号認定 110</v>
       </c>
       <c r="M89" t="str">
-        <v>1号認定 満3歳児～、2・3号認定 おおむね2か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 おおむね3か月～</v>
       </c>
       <c r="N89" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O89" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P89" t="str">
         <v>19:00</v>
@@ -5380,30 +5380,30 @@
         <v/>
       </c>
       <c r="R89" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B90" t="str">
-        <v>34.2734776</v>
+        <v>34.3064057</v>
       </c>
       <c r="C90" t="str">
-        <v>134.1024882</v>
+        <v>134.042294</v>
       </c>
       <c r="D90" t="str">
-        <v>幼保連携型カナン十河こども園</v>
+        <v>幼保連携型認定こども園高松和貴こども園</v>
       </c>
       <c r="E90" t="str">
-        <v>高松市十川西町546-1</v>
+        <v>高松市林町2197-1</v>
       </c>
       <c r="F90" t="str">
-        <v>087-848-0320</v>
+        <v>087-814-4141</v>
       </c>
       <c r="G90" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h48/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h313/</v>
       </c>
       <c r="H90" t="str">
         <v/>
@@ -5418,16 +5418,16 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>1号認定 15、2・3号認定 110</v>
+        <v>1号認定 15、2・3号認定 165</v>
       </c>
       <c r="M90" t="str">
-        <v>1号認定 3歳児～、2・3号認定 おおむね3か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
       </c>
       <c r="N90" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O90" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P90" t="str">
         <v>19:00</v>
@@ -5436,30 +5436,30 @@
         <v/>
       </c>
       <c r="R90" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B91" t="str">
-        <v>34.3064057</v>
+        <v>34.3264572</v>
       </c>
       <c r="C91" t="str">
-        <v>134.042294</v>
+        <v>134.0769366</v>
       </c>
       <c r="D91" t="str">
-        <v>幼保連携型認定こども園高松和貴こども園</v>
+        <v>みらい学園</v>
       </c>
       <c r="E91" t="str">
-        <v>高松市林町2197-1</v>
+        <v>高松市木太町3429-3</v>
       </c>
       <c r="F91" t="str">
-        <v>087-814-4141</v>
+        <v>087-899-2305</v>
       </c>
       <c r="G91" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h313/</v>
+        <v/>
       </c>
       <c r="H91" t="str">
         <v/>
@@ -5474,16 +5474,16 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>1号認定 15、2・3号認定 165</v>
+        <v>1号認定 15、2・3号認定 75</v>
       </c>
       <c r="M91" t="str">
-        <v>1号認定 3歳児～、2・3号認定 3か月～</v>
+        <v>1号認定 3歳児～、2・3号認定 6か月～</v>
       </c>
       <c r="N91" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O91" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P91" t="str">
         <v>19:00</v>
@@ -5497,31 +5497,31 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B92" t="str">
-        <v>34.3264572</v>
+        <v>34.353781</v>
       </c>
       <c r="C92" t="str">
-        <v>134.0769366</v>
+        <v>134.091115</v>
       </c>
       <c r="D92" t="str">
-        <v>みらい学園</v>
+        <v>認定こども園やしま幼稚園</v>
       </c>
       <c r="E92" t="str">
-        <v>高松市木太町3429-3</v>
+        <v>高松市屋島西町2477-4</v>
       </c>
       <c r="F92" t="str">
-        <v>087-899-2305</v>
+        <v>087-843-2241</v>
       </c>
       <c r="G92" t="str">
-        <v/>
+        <v>https://kagawa-colorful.com/hoikusyo/h149</v>
       </c>
       <c r="H92" t="str">
         <v/>
       </c>
       <c r="I92" t="str">
-        <v>認定こども園（幼保連携型）</v>
+        <v>認定こども園（幼稚園型）</v>
       </c>
       <c r="J92" t="str">
         <v/>
@@ -5530,19 +5530,19 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>1号認定 15、2・3号認定 75</v>
+        <v>1号認定 120、2・3号認定 120</v>
       </c>
       <c r="M92" t="str">
-        <v>1号認定 3歳児～、2・3号認定 6か月～</v>
+        <v>1号認定 満3歳～、2・3号認定 14か月～</v>
       </c>
       <c r="N92" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O92" t="str">
-        <v>07:30</v>
+        <v>07:45</v>
       </c>
       <c r="P92" t="str">
-        <v>19:00</v>
+        <v>18:45</v>
       </c>
       <c r="Q92" t="str">
         <v/>
@@ -5553,25 +5553,25 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B93" t="str">
-        <v>34.353781</v>
+        <v>34.338923</v>
       </c>
       <c r="C93" t="str">
-        <v>134.091115</v>
+        <v>134.031483</v>
       </c>
       <c r="D93" t="str">
-        <v>認定こども園やしま幼稚園</v>
+        <v>高松聖ヤコブ幼稚園</v>
       </c>
       <c r="E93" t="str">
-        <v>高松市屋島西町2477-4</v>
+        <v>高松市西宝町二丁目3-14</v>
       </c>
       <c r="F93" t="str">
-        <v>087-843-2241</v>
+        <v>087-861-0425</v>
       </c>
       <c r="G93" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h149</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h249</v>
       </c>
       <c r="H93" t="str">
         <v/>
@@ -5586,19 +5586,19 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>1号認定 120、2・3号認定 120</v>
+        <v>1号認定 130、2号認定 20</v>
       </c>
       <c r="M93" t="str">
-        <v>1号認定 満3歳～、2・3号認定 14か月～</v>
+        <v>1号認定 満3歳～、2号認定 3歳児～</v>
       </c>
       <c r="N93" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O93" t="str">
-        <v>07:45</v>
+        <v>07:30</v>
       </c>
       <c r="P93" t="str">
-        <v>18:45</v>
+        <v>18:30</v>
       </c>
       <c r="Q93" t="str">
         <v/>
@@ -5609,25 +5609,25 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B94" t="str">
-        <v>34.338923</v>
+        <v>34.338702</v>
       </c>
       <c r="C94" t="str">
-        <v>134.031483</v>
+        <v>134.038281</v>
       </c>
       <c r="D94" t="str">
-        <v>高松聖ヤコブ幼稚園</v>
+        <v>認定こども園亀阜幼稚園</v>
       </c>
       <c r="E94" t="str">
-        <v>高松市西宝町二丁目3-14</v>
+        <v>宮脇町一丁目2-23</v>
       </c>
       <c r="F94" t="str">
-        <v>087-861-0425</v>
+        <v>087-831-2557</v>
       </c>
       <c r="G94" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h249</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h252</v>
       </c>
       <c r="H94" t="str">
         <v/>
@@ -5642,10 +5642,10 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>1号認定 130、2号認定 20</v>
+        <v>1号認定 109、2・3号認定 99</v>
       </c>
       <c r="M94" t="str">
-        <v>1号認定 満3歳～、2号認定 3歳児～</v>
+        <v>1号認定 満3歳～、2・3号認定 1歳児～</v>
       </c>
       <c r="N94" t="str">
         <v>月火水木金土</v>
@@ -5654,7 +5654,7 @@
         <v>07:30</v>
       </c>
       <c r="P94" t="str">
-        <v>18:30</v>
+        <v>19:00</v>
       </c>
       <c r="Q94" t="str">
         <v/>
@@ -5665,25 +5665,25 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B95" t="str">
-        <v>34.338702</v>
+        <v>34.279836</v>
       </c>
       <c r="C95" t="str">
-        <v>134.038281</v>
+        <v>134.022373</v>
       </c>
       <c r="D95" t="str">
-        <v>認定こども園亀阜幼稚園</v>
+        <v>らく楽寺井幼稚園</v>
       </c>
       <c r="E95" t="str">
-        <v>宮脇町一丁目2-23</v>
+        <v>高松市寺井町1369-4</v>
       </c>
       <c r="F95" t="str">
-        <v>087-831-2557</v>
+        <v>087-885-2038</v>
       </c>
       <c r="G95" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h252</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h264</v>
       </c>
       <c r="H95" t="str">
         <v/>
@@ -5698,10 +5698,10 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>1号認定 109、2・3号認定 99</v>
+        <v>1号認定 112、2・3号認定 128</v>
       </c>
       <c r="M95" t="str">
-        <v>1号認定 満3歳～、2・3号認定 1歳児～</v>
+        <v>1号認定 満3歳～、2・3号認定 3か月～</v>
       </c>
       <c r="N95" t="str">
         <v>月火水木金土</v>
@@ -5721,25 +5721,25 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B96" t="str">
-        <v>34.279836</v>
+        <v>34.334019</v>
       </c>
       <c r="C96" t="str">
-        <v>134.022373</v>
+        <v>134.114815</v>
       </c>
       <c r="D96" t="str">
-        <v>らく楽寺井幼稚園</v>
+        <v>幼稚園型認定こども園つくし幼稚園</v>
       </c>
       <c r="E96" t="str">
-        <v>高松市寺井町1369-4</v>
+        <v>高松市高松町1711-7</v>
       </c>
       <c r="F96" t="str">
-        <v>087-885-2038</v>
+        <v>087-843-4484</v>
       </c>
       <c r="G96" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h264</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h272/</v>
       </c>
       <c r="H96" t="str">
         <v/>
@@ -5754,10 +5754,10 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>1号認定 112、2・3号認定 128</v>
+        <v>1号認定 150、2・3号認定 110</v>
       </c>
       <c r="M96" t="str">
-        <v>1号認定 満3歳～、2・3号認定 3か月～</v>
+        <v>1号認定 満3歳～、2・3号認定 15か月～</v>
       </c>
       <c r="N96" t="str">
         <v>月火水木金土</v>
@@ -5772,30 +5772,30 @@
         <v/>
       </c>
       <c r="R96" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B97" t="str">
-        <v>34.334019</v>
+        <v>34.304505</v>
       </c>
       <c r="C97" t="str">
-        <v>134.114815</v>
+        <v>134.021922</v>
       </c>
       <c r="D97" t="str">
-        <v>幼稚園型認定こども園つくし幼稚園</v>
+        <v>認定こども園勅使百華幼稚園</v>
       </c>
       <c r="E97" t="str">
-        <v>高松市高松町1711-7</v>
+        <v>高松市勅使町955</v>
       </c>
       <c r="F97" t="str">
-        <v>087-843-4484</v>
+        <v>087-865-9419</v>
       </c>
       <c r="G97" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h272/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h273/</v>
       </c>
       <c r="H97" t="str">
         <v/>
@@ -5810,10 +5810,10 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>1号認定 150、2・3号認定 110</v>
+        <v>1号認定 217、2・3号認定 99</v>
       </c>
       <c r="M97" t="str">
-        <v>1号認定 満3歳～、2・3号認定 15か月～</v>
+        <v>1号認定 満3歳～、2・3号認定 16か月～（4.1時点1歳児）</v>
       </c>
       <c r="N97" t="str">
         <v>月火水木金土</v>
@@ -5822,42 +5822,42 @@
         <v>07:30</v>
       </c>
       <c r="P97" t="str">
-        <v>19:00</v>
+        <v>18:30</v>
       </c>
       <c r="Q97" t="str">
         <v/>
       </c>
       <c r="R97" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B98" t="str">
-        <v>34.304505</v>
+        <v>34.332072</v>
       </c>
       <c r="C98" t="str">
-        <v>134.021922</v>
+        <v>134.049227</v>
       </c>
       <c r="D98" t="str">
-        <v>認定こども園勅使百華幼稚園</v>
+        <v>栗林にこにこ保育園</v>
       </c>
       <c r="E98" t="str">
-        <v>高松市勅使町955</v>
+        <v>高松市栗林町二丁目3-2</v>
       </c>
       <c r="F98" t="str">
-        <v>087-865-9419</v>
+        <v>087-831-1319</v>
       </c>
       <c r="G98" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h273/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/%25E6%25A0%2597%25E6%259E%2597%25E3%2581%25AB%25E3%2581%2593%25E3%2581%25AB%25E3%2581%2593%25E4%25BF%259D%25E8%2582%25B2%25E5%259C%2592/</v>
       </c>
       <c r="H98" t="str">
         <v/>
       </c>
       <c r="I98" t="str">
-        <v>認定こども園（幼稚園型）</v>
+        <v>地域型保育事業（小規模保育事業A型）</v>
       </c>
       <c r="J98" t="str">
         <v/>
@@ -5866,10 +5866,10 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>1号認定 217、2・3号認定 99</v>
+        <v>12</v>
       </c>
       <c r="M98" t="str">
-        <v>1号認定 満3歳～、2・3号認定 16か月～（4.1時点1歳児）</v>
+        <v>おおむね2か月～2歳児</v>
       </c>
       <c r="N98" t="str">
         <v>月火水木金土</v>
@@ -5878,36 +5878,36 @@
         <v>07:30</v>
       </c>
       <c r="P98" t="str">
-        <v>18:30</v>
+        <v>19:00</v>
       </c>
       <c r="Q98" t="str">
         <v/>
       </c>
       <c r="R98" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B99" t="str">
-        <v>34.332072</v>
+        <v>34.332365</v>
       </c>
       <c r="C99" t="str">
-        <v>134.049227</v>
+        <v>134.097201</v>
       </c>
       <c r="D99" t="str">
-        <v>栗林にこにこ保育園</v>
+        <v>小規模保育所もも</v>
       </c>
       <c r="E99" t="str">
-        <v>高松市栗林町二丁目3-2</v>
+        <v>高松市春日町1176</v>
       </c>
       <c r="F99" t="str">
-        <v>087-831-1319</v>
+        <v>087-843-8255</v>
       </c>
       <c r="G99" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/%25E6%25A0%2597%25E6%259E%2597%25E3%2581%25AB%25E3%2581%2593%25E3%2581%25AB%25E3%2581%2593%25E4%25BF%259D%25E8%2582%25B2%25E5%259C%2592/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/%25E5%25B0%258F%25E8%25A6%258F%25E6%25A8%25A1%25E4%25BF%259D%25E8%2582%25B2%25E6%2589%2580%25E3%2580%2580%25E3%2582%2582%25E3%2582%2582/</v>
       </c>
       <c r="H99" t="str">
         <v/>
@@ -5922,10 +5922,10 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M99" t="str">
-        <v>おおむね2か月～2歳児</v>
+        <v>2か月～2歳児</v>
       </c>
       <c r="N99" t="str">
         <v>月火水木金土</v>
@@ -5934,36 +5934,36 @@
         <v>07:30</v>
       </c>
       <c r="P99" t="str">
-        <v>19:00</v>
+        <v>18:30</v>
       </c>
       <c r="Q99" t="str">
         <v/>
       </c>
       <c r="R99" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B100" t="str">
-        <v>34.332365</v>
+        <v>34.288288</v>
       </c>
       <c r="C100" t="str">
-        <v>134.097201</v>
+        <v>134.059379</v>
       </c>
       <c r="D100" t="str">
-        <v>小規模保育所もも</v>
+        <v>らく楽多肥保育園</v>
       </c>
       <c r="E100" t="str">
-        <v>高松市春日町1176</v>
+        <v>高松市多肥上町1713</v>
       </c>
       <c r="F100" t="str">
-        <v>087-843-8255</v>
+        <v>087-816-8301</v>
       </c>
       <c r="G100" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/%25E5%25B0%258F%25E8%25A6%258F%25E6%25A8%25A1%25E4%25BF%259D%25E8%2582%25B2%25E6%2589%2580%25E3%2580%2580%25E3%2582%2582%25E3%2582%2582/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/らく楽多肥保育園/</v>
       </c>
       <c r="H100" t="str">
         <v/>
@@ -5978,10 +5978,10 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M100" t="str">
-        <v>2か月～2歳児</v>
+        <v>3か月～2歳児</v>
       </c>
       <c r="N100" t="str">
         <v>月火水木金土</v>
@@ -6001,25 +6001,25 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B101" t="str">
-        <v>34.288288</v>
+        <v>34.316351</v>
       </c>
       <c r="C101" t="str">
-        <v>134.059379</v>
+        <v>134.073388</v>
       </c>
       <c r="D101" t="str">
-        <v>らく楽多肥保育園</v>
+        <v>ソラ小規模保育園たかまつ</v>
       </c>
       <c r="E101" t="str">
-        <v>高松市多肥上町1713</v>
+        <v>高松市木太町9区786-2</v>
       </c>
       <c r="F101" t="str">
-        <v>087-816-8301</v>
+        <v>087-816-5150</v>
       </c>
       <c r="G101" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/らく楽多肥保育園/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/ソラ小規模保育園たかまつ/</v>
       </c>
       <c r="H101" t="str">
         <v/>
@@ -6034,19 +6034,19 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M101" t="str">
-        <v>3か月～2歳児</v>
+        <v>54日～2歳児</v>
       </c>
       <c r="N101" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O101" t="str">
-        <v>07:30</v>
+        <v>07:00</v>
       </c>
       <c r="P101" t="str">
-        <v>18:30</v>
+        <v>19:00</v>
       </c>
       <c r="Q101" t="str">
         <v/>
@@ -6057,25 +6057,25 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B102" t="str">
-        <v>34.316351</v>
+        <v>34.303424</v>
       </c>
       <c r="C102" t="str">
-        <v>134.073388</v>
+        <v>134.060713</v>
       </c>
       <c r="D102" t="str">
-        <v>ソラ小規模保育園たかまつ</v>
+        <v>ニチイキッズたひ東保育園</v>
       </c>
       <c r="E102" t="str">
-        <v>高松市木太町9区786-2</v>
+        <v>高松市多肥下町1533-3</v>
       </c>
       <c r="F102" t="str">
-        <v>087-816-5150</v>
+        <v>087-864-3133</v>
       </c>
       <c r="G102" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/ソラ小規模保育園たかまつ/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/ニチイキッズたひ東/</v>
       </c>
       <c r="H102" t="str">
         <v/>
@@ -6093,16 +6093,16 @@
         <v>19</v>
       </c>
       <c r="M102" t="str">
-        <v>54日～2歳児</v>
+        <v>2か月～2歳児</v>
       </c>
       <c r="N102" t="str">
         <v>月火水木金土</v>
       </c>
       <c r="O102" t="str">
-        <v>07:00</v>
+        <v>07:30</v>
       </c>
       <c r="P102" t="str">
-        <v>19:00</v>
+        <v>19:30</v>
       </c>
       <c r="Q102" t="str">
         <v/>
@@ -6113,25 +6113,25 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B103" t="str">
-        <v>34.303424</v>
+        <v>34.298947</v>
       </c>
       <c r="C103" t="str">
-        <v>134.060713</v>
+        <v>134.055734</v>
       </c>
       <c r="D103" t="str">
-        <v>ニチイキッズたひ東保育園</v>
+        <v>ニチイキッズたひ西保育園</v>
       </c>
       <c r="E103" t="str">
-        <v>高松市多肥下町1533-3</v>
+        <v>高松市多肥下町1581-6</v>
       </c>
       <c r="F103" t="str">
-        <v>087-864-3133</v>
+        <v>087-815-0224</v>
       </c>
       <c r="G103" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/ニチイキッズたひ東/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/ニチイキッズたひ西/</v>
       </c>
       <c r="H103" t="str">
         <v/>
@@ -6169,25 +6169,25 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B104" t="str">
-        <v>34.298947</v>
+        <v>34.37717</v>
       </c>
       <c r="C104" t="str">
-        <v>134.055734</v>
+        <v>134.122418</v>
       </c>
       <c r="D104" t="str">
-        <v>ニチイキッズたひ西保育園</v>
+        <v>おるごーる</v>
       </c>
       <c r="E104" t="str">
-        <v>高松市多肥下町1581-6</v>
+        <v>高松市庵治町156-36</v>
       </c>
       <c r="F104" t="str">
-        <v>087-815-0224</v>
+        <v>087-871-3503</v>
       </c>
       <c r="G104" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/ニチイキッズたひ西/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/オルゴール/</v>
       </c>
       <c r="H104" t="str">
         <v/>
@@ -6202,10 +6202,10 @@
         <v/>
       </c>
       <c r="L104" t="str">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="M104" t="str">
-        <v>2か月～2歳児</v>
+        <v>おおむね3か月～2歳児</v>
       </c>
       <c r="N104" t="str">
         <v>月火水木金土</v>
@@ -6214,7 +6214,7 @@
         <v>07:30</v>
       </c>
       <c r="P104" t="str">
-        <v>19:30</v>
+        <v>18:30</v>
       </c>
       <c r="Q104" t="str">
         <v/>
@@ -6225,25 +6225,25 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B105" t="str">
-        <v>34.37717</v>
+        <v>34.2899</v>
       </c>
       <c r="C105" t="str">
-        <v>134.122418</v>
+        <v>134.05856</v>
       </c>
       <c r="D105" t="str">
-        <v>おるごーる</v>
+        <v>にじいろうさぎ保育園</v>
       </c>
       <c r="E105" t="str">
-        <v>高松市庵治町156-36</v>
+        <v>高松市多肥上町1622-13</v>
       </c>
       <c r="F105" t="str">
-        <v>087-871-3503</v>
+        <v>087-889-3711</v>
       </c>
       <c r="G105" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/オルゴール/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/にじいろうさぎ保育園/</v>
       </c>
       <c r="H105" t="str">
         <v/>
@@ -6258,10 +6258,10 @@
         <v/>
       </c>
       <c r="L105" t="str">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M105" t="str">
-        <v>おおむね3か月～2歳児</v>
+        <v>おおむね2か月～2歳児</v>
       </c>
       <c r="N105" t="str">
         <v>月火水木金土</v>
@@ -6281,25 +6281,25 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B106" t="str">
-        <v>34.2899</v>
+        <v>34.336075</v>
       </c>
       <c r="C106" t="str">
-        <v>134.05856</v>
+        <v>134.072522</v>
       </c>
       <c r="D106" t="str">
-        <v>にじいろうさぎ保育園</v>
+        <v>木太にこにこ保育園</v>
       </c>
       <c r="E106" t="str">
-        <v>高松市多肥上町1622-13</v>
+        <v>高松市木太町2321-1</v>
       </c>
       <c r="F106" t="str">
-        <v>087-889-3711</v>
+        <v>087-837-5330</v>
       </c>
       <c r="G106" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/にじいろうさぎ保育園/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/木太にこにこ保育園/</v>
       </c>
       <c r="H106" t="str">
         <v/>
@@ -6314,7 +6314,7 @@
         <v/>
       </c>
       <c r="L106" t="str">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M106" t="str">
         <v>おおむね2か月～2歳児</v>
@@ -6326,36 +6326,36 @@
         <v>07:30</v>
       </c>
       <c r="P106" t="str">
-        <v>18:30</v>
+        <v>19:00</v>
       </c>
       <c r="Q106" t="str">
         <v/>
       </c>
       <c r="R106" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B107" t="str">
-        <v>34.336075</v>
+        <v>34.311371</v>
       </c>
       <c r="C107" t="str">
-        <v>134.072522</v>
+        <v>134.055948</v>
       </c>
       <c r="D107" t="str">
-        <v>木太にこにこ保育園</v>
+        <v>伏石にこにこ保育園</v>
       </c>
       <c r="E107" t="str">
-        <v>高松市木太町2321-1</v>
+        <v>高松市伏石町2100-1</v>
       </c>
       <c r="F107" t="str">
-        <v>087-837-5330</v>
+        <v>087-868-3339</v>
       </c>
       <c r="G107" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/木太にこにこ保育園/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/伏石にこにこ保育園/</v>
       </c>
       <c r="H107" t="str">
         <v/>
@@ -6393,25 +6393,25 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B108" t="str">
-        <v>34.311371</v>
+        <v>34.316136</v>
       </c>
       <c r="C108" t="str">
-        <v>134.055948</v>
+        <v>134.061202</v>
       </c>
       <c r="D108" t="str">
-        <v>伏石にこにこ保育園</v>
+        <v>ニチイキッズまつなわ西保育園</v>
       </c>
       <c r="E108" t="str">
-        <v>高松市伏石町2100-1</v>
+        <v>高松市松縄町1118-8</v>
       </c>
       <c r="F108" t="str">
-        <v>087-868-3339</v>
+        <v>087-864-3155</v>
       </c>
       <c r="G108" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/伏石にこにこ保育園/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/ニチイキッズまつなわ西保育園/</v>
       </c>
       <c r="H108" t="str">
         <v/>
@@ -6426,10 +6426,10 @@
         <v/>
       </c>
       <c r="L108" t="str">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M108" t="str">
-        <v>おおむね2か月～2歳児</v>
+        <v>2か月～2歳児</v>
       </c>
       <c r="N108" t="str">
         <v>月火水木金土</v>
@@ -6438,36 +6438,36 @@
         <v>07:30</v>
       </c>
       <c r="P108" t="str">
-        <v>19:00</v>
+        <v>19:30</v>
       </c>
       <c r="Q108" t="str">
         <v/>
       </c>
       <c r="R108" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B109" t="str">
-        <v>34.316136</v>
+        <v>34.3049893</v>
       </c>
       <c r="C109" t="str">
-        <v>134.061202</v>
+        <v>134.0560416</v>
       </c>
       <c r="D109" t="str">
-        <v>ニチイキッズまつなわ西保育園</v>
+        <v>太田にこにこ保育園</v>
       </c>
       <c r="E109" t="str">
-        <v>高松市松縄町1118-8</v>
+        <v>高松市太田下町3026-13</v>
       </c>
       <c r="F109" t="str">
-        <v>087-864-3155</v>
+        <v>087-868-2355</v>
       </c>
       <c r="G109" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/ニチイキッズまつなわ西保育園/</v>
+        <v>https://kagawa-colorful.com/hoikusho/%E5%A4%AA%E7%94%B0%E3%81%AB%E3%81%93%E3%81%AB%E3%81%93%E4%BF%9D%E8%82%B2%E5%9C%92/</v>
       </c>
       <c r="H109" t="str">
         <v/>
@@ -6485,7 +6485,7 @@
         <v>19</v>
       </c>
       <c r="M109" t="str">
-        <v>2か月～2歳児</v>
+        <v>おおむね2か月～2歳児</v>
       </c>
       <c r="N109" t="str">
         <v>月火水木金土</v>
@@ -6494,36 +6494,36 @@
         <v>07:30</v>
       </c>
       <c r="P109" t="str">
-        <v>19:30</v>
+        <v>19:00</v>
       </c>
       <c r="Q109" t="str">
         <v/>
       </c>
       <c r="R109" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B110" t="str">
-        <v>34.3049893</v>
+        <v>34.2989616</v>
       </c>
       <c r="C110" t="str">
-        <v>134.0560416</v>
+        <v>134.0640027</v>
       </c>
       <c r="D110" t="str">
-        <v>太田にこにこ保育園</v>
+        <v>林にこにこ保育園</v>
       </c>
       <c r="E110" t="str">
-        <v>高松市太田下町3026-13</v>
+        <v>高松市林町252-1</v>
       </c>
       <c r="F110" t="str">
-        <v>087-868-2355</v>
+        <v>087-868-0103</v>
       </c>
       <c r="G110" t="str">
-        <v>https://kagawa-colorful.com/hoikusho/%E5%A4%AA%E7%94%B0%E3%81%AB%E3%81%93%E3%81%AB%E3%81%93%E4%BF%9D%E8%82%B2%E5%9C%92/</v>
+        <v>https://kagawa-colorful.com/hoikusho/%E6%9E%97%E3%81%AB%E3%81%93%E3%81%AB%E3%81%93%E4%BF%9D%E8%82%B2%E5%9C%92/</v>
       </c>
       <c r="H110" t="str">
         <v/>
@@ -6561,25 +6561,25 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B111" t="str">
-        <v>34.2989616</v>
+        <v>34.2612106</v>
       </c>
       <c r="C111" t="str">
-        <v>134.0640027</v>
+        <v>134.0367875</v>
       </c>
       <c r="D111" t="str">
-        <v>林にこにこ保育園</v>
+        <v>みいろ</v>
       </c>
       <c r="E111" t="str">
-        <v>高松市林町252-1</v>
+        <v>高松市香川町浅野668-5</v>
       </c>
       <c r="F111" t="str">
-        <v>087-868-0103</v>
+        <v>087-880-3274</v>
       </c>
       <c r="G111" t="str">
-        <v>https://kagawa-colorful.com/hoikusho/%E6%9E%97%E3%81%AB%E3%81%93%E3%81%AB%E3%81%93%E4%BF%9D%E8%82%B2%E5%9C%92/</v>
+        <v>https://kagawa-colorful.com/hoikusho/%E4%BF%9D%E8%82%B2%E3%81%AE%E5%AE%B6%E3%81%BF%E3%81%84%E3%82%8D/</v>
       </c>
       <c r="H111" t="str">
         <v/>
@@ -6594,10 +6594,10 @@
         <v/>
       </c>
       <c r="L111" t="str">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M111" t="str">
-        <v>おおむね2か月～2歳児</v>
+        <v>３か月～2歳児</v>
       </c>
       <c r="N111" t="str">
         <v>月火水木金土</v>
@@ -6606,7 +6606,7 @@
         <v>07:30</v>
       </c>
       <c r="P111" t="str">
-        <v>19:00</v>
+        <v>18:30</v>
       </c>
       <c r="Q111" t="str">
         <v/>
@@ -6617,25 +6617,25 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B112" t="str">
-        <v>34.2612106</v>
+        <v>34.3389027</v>
       </c>
       <c r="C112" t="str">
-        <v>134.0367875</v>
+        <v>134.052851</v>
       </c>
       <c r="D112" t="str">
-        <v>みいろ</v>
+        <v>瓦町FLAG保育園</v>
       </c>
       <c r="E112" t="str">
-        <v>高松市香川町浅野668-5</v>
+        <v>高松市常磐町一丁目3-1瓦町FLAG1F</v>
       </c>
       <c r="F112" t="str">
-        <v>087-880-3274</v>
+        <v>087-802-6966</v>
       </c>
       <c r="G112" t="str">
-        <v>https://kagawa-colorful.com/hoikusho/%E4%BF%9D%E8%82%B2%E3%81%AE%E5%AE%B6%E3%81%BF%E3%81%84%E3%82%8D/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/%E7%93%A6%E7%94%BAFLAG%E4%BF%9D%E8%82%B2%E5%9C%92/</v>
       </c>
       <c r="H112" t="str">
         <v/>
@@ -6650,7 +6650,7 @@
         <v/>
       </c>
       <c r="L112" t="str">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M112" t="str">
         <v>３か月～2歳児</v>
@@ -6662,42 +6662,42 @@
         <v>07:30</v>
       </c>
       <c r="P112" t="str">
-        <v>18:30</v>
+        <v>19:00</v>
       </c>
       <c r="Q112" t="str">
         <v/>
       </c>
       <c r="R112" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B113" t="str">
-        <v>34.3389027</v>
+        <v>34.340379</v>
       </c>
       <c r="C113" t="str">
-        <v>134.052851</v>
+        <v>134.044986</v>
       </c>
       <c r="D113" t="str">
-        <v>瓦町FLAG保育園</v>
+        <v>保育所てふてふ</v>
       </c>
       <c r="E113" t="str">
-        <v>高松市常磐町一丁目3-1瓦町FLAG1F</v>
+        <v>高松市天神前5-6 高松メディカルモール2階・4階</v>
       </c>
       <c r="F113" t="str">
-        <v>087-802-6966</v>
+        <v>087-813-0218</v>
       </c>
       <c r="G113" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/%E7%93%A6%E7%94%BAFLAG%E4%BF%9D%E8%82%B2%E5%9C%92/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/院内保育所　てふてふ/</v>
       </c>
       <c r="H113" t="str">
         <v/>
       </c>
       <c r="I113" t="str">
-        <v>地域型保育事業（小規模保育事業A型）</v>
+        <v>地域型保育事業（事業所内保育事業）</v>
       </c>
       <c r="J113" t="str">
         <v/>
@@ -6706,10 +6706,10 @@
         <v/>
       </c>
       <c r="L113" t="str">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="M113" t="str">
-        <v>３か月～2歳児</v>
+        <v>6か月～2歳児</v>
       </c>
       <c r="N113" t="str">
         <v>月火水木金土</v>
@@ -6729,25 +6729,25 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B114" t="str">
-        <v>34.340379</v>
+        <v>34.31871165074609</v>
       </c>
       <c r="C114" t="str">
-        <v>134.044986</v>
+        <v>134.04616290974917</v>
       </c>
       <c r="D114" t="str">
-        <v>保育所てふてふ</v>
+        <v>小規模保育施設おひさま保育園</v>
       </c>
       <c r="E114" t="str">
-        <v>高松市天神前5-6 高松メディカルモール2階・4階</v>
+        <v xml:space="preserve">高松市三条町４９４番地１　</v>
       </c>
       <c r="F114" t="str">
-        <v>087-813-0218</v>
+        <v>087-899-5565</v>
       </c>
       <c r="G114" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/院内保育所　てふてふ/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/小規模保育所　小規模保育施設おひさま保育園/</v>
       </c>
       <c r="H114" t="str">
         <v/>
@@ -6762,10 +6762,10 @@
         <v/>
       </c>
       <c r="L114" t="str">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="M114" t="str">
-        <v>6か月～2歳児</v>
+        <v>おおむね３か月～2歳児</v>
       </c>
       <c r="N114" t="str">
         <v>月火水木金土</v>
@@ -6785,25 +6785,25 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B115" t="str">
-        <v>34.31871165074609</v>
+        <v>34.297299240412265</v>
       </c>
       <c r="C115" t="str">
-        <v>134.04616290974917</v>
+        <v>134.0574624385844</v>
       </c>
       <c r="D115" t="str">
-        <v>小規模保育施設おひさま保育園</v>
+        <v>スマはぴ保育園　なないろstation</v>
       </c>
       <c r="E115" t="str">
-        <v xml:space="preserve">高松市三条町４９４番地１　</v>
+        <v xml:space="preserve">高松市多肥上町１３０1番地３　</v>
       </c>
       <c r="F115" t="str">
-        <v>087-899-5565</v>
+        <v>090-2373-7716</v>
       </c>
       <c r="G115" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/小規模保育所　小規模保育施設おひさま保育園/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/小規模保育所　スマはぴ保育園なないろstation/</v>
       </c>
       <c r="H115" t="str">
         <v/>
@@ -6821,7 +6821,7 @@
         <v>18</v>
       </c>
       <c r="M115" t="str">
-        <v>おおむね３か月～2歳児</v>
+        <v>３か月～2歳児</v>
       </c>
       <c r="N115" t="str">
         <v>月火水木金土</v>
@@ -6836,30 +6836,30 @@
         <v/>
       </c>
       <c r="R115" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B116" t="str">
-        <v>34.297299240412265</v>
+        <v>34.309844386262995</v>
       </c>
       <c r="C116" t="str">
-        <v>134.0574624385844</v>
+        <v>134.04623465392953</v>
       </c>
       <c r="D116" t="str">
-        <v>スマはぴ保育園　なないろstation</v>
+        <v>にこにこ保育教育研究センター　附属保育園すくすく</v>
       </c>
       <c r="E116" t="str">
-        <v xml:space="preserve">高松市多肥上町１３０1番地３　</v>
+        <v>高松市太田下町２３５０番地１</v>
       </c>
       <c r="F116" t="str">
-        <v>090-2373-7716</v>
+        <v>087-802-5361</v>
       </c>
       <c r="G116" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/小規模保育所　スマはぴ保育園なないろstation/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/小規模保育所　にこにこ保育教育研究センター附属保育園すくすく/</v>
       </c>
       <c r="H116" t="str">
         <v/>
@@ -6874,10 +6874,10 @@
         <v/>
       </c>
       <c r="L116" t="str">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M116" t="str">
-        <v>３か月～2歳児</v>
+        <v>おおむね2か月～2歳児</v>
       </c>
       <c r="N116" t="str">
         <v>月火水木金土</v>
@@ -6897,25 +6897,25 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B117" t="str">
-        <v>34.309844386262995</v>
+        <v>34.3097729899615</v>
       </c>
       <c r="C117" t="str">
-        <v>134.04623465392953</v>
+        <v>134.0461698809127</v>
       </c>
       <c r="D117" t="str">
-        <v>にこにこ保育教育研究センター　附属保育園すくすく</v>
+        <v>にこにこ保育教育研究センター　附属保育園わくわく</v>
       </c>
       <c r="E117" t="str">
         <v>高松市太田下町２３５０番地１</v>
       </c>
       <c r="F117" t="str">
-        <v>087-802-5361</v>
+        <v>087-802-5362</v>
       </c>
       <c r="G117" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/小規模保育所　にこにこ保育教育研究センター附属保育園すくすく/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/小規模保育所　にこにこ保育教育研究センター附属保育園わくわく/</v>
       </c>
       <c r="H117" t="str">
         <v/>
@@ -6953,25 +6953,25 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B118" t="str">
-        <v>34.3097729899615</v>
+        <v>34.27968265221049</v>
       </c>
       <c r="C118" t="str">
-        <v>134.0461698809127</v>
+        <v>134.02278072883618</v>
       </c>
       <c r="D118" t="str">
-        <v>にこにこ保育教育研究センター　附属保育園わくわく</v>
+        <v>らく楽寺井保育園</v>
       </c>
       <c r="E118" t="str">
-        <v>高松市太田下町２３５０番地１</v>
+        <v>高松市寺井町１３６４番地２５</v>
       </c>
       <c r="F118" t="str">
-        <v>087-802-5362</v>
+        <v>087-885-6002</v>
       </c>
       <c r="G118" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/小規模保育所　にこにこ保育教育研究センター附属保育園わくわく/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/小規模保育所　らく楽寺井保育園/</v>
       </c>
       <c r="H118" t="str">
         <v/>
@@ -6986,10 +6986,10 @@
         <v/>
       </c>
       <c r="L118" t="str">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M118" t="str">
-        <v>おおむね2か月～2歳児</v>
+        <v>３か月～2歳児</v>
       </c>
       <c r="N118" t="str">
         <v>月火水木金土</v>
@@ -7004,36 +7004,36 @@
         <v/>
       </c>
       <c r="R118" t="str">
-        <v>有</v>
+        <v>無</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B119" t="str">
-        <v>34.27968265221049</v>
+        <v>34.30287</v>
       </c>
       <c r="C119" t="str">
-        <v>134.02278072883618</v>
+        <v>134.016075</v>
       </c>
       <c r="D119" t="str">
-        <v>らく楽寺井保育園</v>
+        <v>メリーＧＯランド高松園</v>
       </c>
       <c r="E119" t="str">
-        <v>高松市寺井町１３６４番地２５</v>
+        <v>高松市成合町796-1</v>
       </c>
       <c r="F119" t="str">
-        <v>087-885-6002</v>
+        <v>087-886-6669</v>
       </c>
       <c r="G119" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/小規模保育所　らく楽寺井保育園/</v>
+        <v>https://kagawa-colorful.com/hoikusyo/h274/</v>
       </c>
       <c r="H119" t="str">
         <v/>
       </c>
       <c r="I119" t="str">
-        <v>地域型保育事業（事業所内保育事業）</v>
+        <v>認定こども園（地方裁量型）</v>
       </c>
       <c r="J119" t="str">
         <v/>
@@ -7042,10 +7042,10 @@
         <v/>
       </c>
       <c r="L119" t="str">
-        <v>18</v>
+        <v>1号認定 20、2・3号認定 35</v>
       </c>
       <c r="M119" t="str">
-        <v>３か月～2歳児</v>
+        <v>1号認定 満3歳～、2・3号認定 1歳半～</v>
       </c>
       <c r="N119" t="str">
         <v>月火水木金土</v>
@@ -7054,54 +7054,45 @@
         <v>07:30</v>
       </c>
       <c r="P119" t="str">
-        <v>19:00</v>
+        <v>18:00</v>
       </c>
       <c r="Q119" t="str">
         <v/>
       </c>
       <c r="R119" t="str">
-        <v>無</v>
+        <v>有</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B120" t="str">
-        <v>34.30287</v>
+        <v>34.3407151783048</v>
       </c>
       <c r="C120" t="str">
-        <v>134.016075</v>
+        <v xml:space="preserve">134.05261279566935 </v>
       </c>
       <c r="D120" t="str">
-        <v>メリーＧＯランド高松園</v>
+        <v>認定こども園光華幼稚園</v>
       </c>
       <c r="E120" t="str">
-        <v>高松市成合町796-1</v>
+        <v>高松市瓦町１丁目１３−８</v>
       </c>
       <c r="F120" t="str">
-        <v>087-886-6669</v>
+        <v>087-831-5011</v>
       </c>
       <c r="G120" t="str">
-        <v>https://kagawa-colorful.com/hoikusyo/h274/</v>
-      </c>
-      <c r="H120" t="str">
-        <v/>
+        <v>http://www.kohka.ed.jp/</v>
       </c>
       <c r="I120" t="str">
-        <v>認定こども園（地方裁量型）</v>
-      </c>
-      <c r="J120" t="str">
-        <v/>
-      </c>
-      <c r="K120" t="str">
-        <v/>
+        <v>認定こども園(幼稚園型)</v>
       </c>
       <c r="L120" t="str">
-        <v>1号認定 20、2・3号認定 35</v>
+        <v>262</v>
       </c>
       <c r="M120" t="str">
-        <v>1号認定 満3歳～、2・3号認定 1歳半～</v>
+        <v>1号認定 満3歳～、2・3号認定 3か月～</v>
       </c>
       <c r="N120" t="str">
         <v>月火水木金土</v>
@@ -7110,18 +7101,159 @@
         <v>07:30</v>
       </c>
       <c r="P120" t="str">
-        <v>18:00</v>
-      </c>
-      <c r="Q120" t="str">
-        <v/>
+        <v>18:30</v>
       </c>
       <c r="R120" t="str">
+        <v>無</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>128</v>
+      </c>
+      <c r="B121" t="str">
+        <v>34.34514634755434</v>
+      </c>
+      <c r="C121" t="str">
+        <v>134.09535423984784</v>
+      </c>
+      <c r="D121" t="str">
+        <v>認定こども園屋島協会幼稚園</v>
+      </c>
+      <c r="E121" t="str">
+        <v>高松市屋島屋島西町１３９２−７</v>
+      </c>
+      <c r="F121" t="str">
+        <v>087-841-1925</v>
+      </c>
+      <c r="G121" t="str">
+        <v>http://www.akaiyane.jp/</v>
+      </c>
+      <c r="H121" t="str">
+        <v/>
+      </c>
+      <c r="I121" t="str">
+        <v>認定こども園(幼稚園型)</v>
+      </c>
+      <c r="J121" t="str">
+        <v/>
+      </c>
+      <c r="K121" t="str">
+        <v/>
+      </c>
+      <c r="L121" t="str">
+        <v>94</v>
+      </c>
+      <c r="M121" t="str">
+        <v>1号認定 満3歳～、2・3号認定 6か月～</v>
+      </c>
+      <c r="N121" t="str">
+        <v>月火水木金土</v>
+      </c>
+      <c r="O121" t="str">
+        <v>07:30</v>
+      </c>
+      <c r="P121" t="str">
+        <v>18:30</v>
+      </c>
+      <c r="Q121" t="str">
+        <v/>
+      </c>
+      <c r="R121" t="str">
+        <v>無</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>129</v>
+      </c>
+      <c r="B122" t="str">
+        <v>34.32278136857088</v>
+      </c>
+      <c r="C122" t="str">
+        <v>134.05279192635362</v>
+      </c>
+      <c r="D122" t="str">
+        <v>認定こども園くにとう幼稚園</v>
+      </c>
+      <c r="E122" t="str">
+        <v>高松市伏石町１６１１</v>
+      </c>
+      <c r="F122" t="str">
+        <v>087-866-1666</v>
+      </c>
+      <c r="G122" t="str">
+        <v>http://www.kunitou.jp/</v>
+      </c>
+      <c r="I122" t="str">
+        <v>認定こども園(幼稚園型)</v>
+      </c>
+      <c r="L122" t="str">
+        <v>390</v>
+      </c>
+      <c r="M122" t="str">
+        <v>1号認定 満3歳～、2・3号認定 1歳児～</v>
+      </c>
+      <c r="N122" t="str">
+        <v>月火水木金土</v>
+      </c>
+      <c r="O122" t="str">
+        <v>07:30</v>
+      </c>
+      <c r="P122" t="str">
+        <v>18:30</v>
+      </c>
+      <c r="R122" t="str">
+        <v>無</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>130</v>
+      </c>
+      <c r="B123" t="str">
+        <v>34.29903238700037</v>
+      </c>
+      <c r="C123" t="str">
+        <v>134.0757202604509</v>
+      </c>
+      <c r="D123" t="str">
+        <v>にこにここども園</v>
+      </c>
+      <c r="E123" t="str">
+        <v>高松市林町２９４−１</v>
+      </c>
+      <c r="F123" t="str">
+        <v>087-813-8300</v>
+      </c>
+      <c r="G123" t="str">
+        <v>https://nikoniko-fukushi.com/niconico/niconico/</v>
+      </c>
+      <c r="I123" t="str">
+        <v>認定こども園(保育所型)</v>
+      </c>
+      <c r="L123" t="str">
+        <v>125</v>
+      </c>
+      <c r="M123" t="str">
+        <v>1号認定 満3歳～、2・3号認定 2か月～</v>
+      </c>
+      <c r="N123" t="str">
+        <v>月火水木金土</v>
+      </c>
+      <c r="O123" t="str">
+        <v>07:30</v>
+      </c>
+      <c r="P123" t="str">
+        <v>19:00</v>
+      </c>
+      <c r="R123" t="str">
         <v>有</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R120"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R123"/>
   </ignoredErrors>
 </worksheet>
 </file>